--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0138A3A1-D155-45D3-A06C-AD0059E8DE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194294E8-D762-4C6A-93FD-65E9EBEA6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="619">
   <si>
     <t>Nome Carta</t>
   </si>
@@ -1869,9 +1869,6 @@
     <t>Piaga: Zanzare del Deserto</t>
   </si>
   <si>
-    <t>Ogni Santo avversario perde 1 Fede. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Piaga: Mosche d'Egitto</t>
   </si>
   <si>
@@ -1881,9 +1878,6 @@
     <t>Piaga: Ulcere della Carne</t>
   </si>
   <si>
-    <t>Scegli fino a 2 Santi avversari: ognuno perde 3 Fede. Poi infliggi 2 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Piaga: Grandine di Fuoco</t>
   </si>
   <si>
@@ -1897,6 +1891,18 @@
   </si>
   <si>
     <t>Una volta per turno, quando questa carta attacca un Santo avversario, puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Portatore delle Piaghe</t>
+  </si>
+  <si>
+    <t>Ogni Santo avversario perde 3 Fede. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Scegli fino a 2 Santi avversari: ognuno perde 4 Fede. Poi infliggi 2 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Questa carta può essere evocata solo scomunicando 3 carte Piaga dalla tua mano o cimitero, senza pagare costo di Ispirazione. Questa carta non può essere bersagliata dagli effetti di altre carte. Una volta per turno, scegli e attiva un effetto di qualsiasi carta "Piaga" benedizione o maledizione.</t>
   </si>
 </sst>
 </file>
@@ -3397,8 +3403,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD0662AD-6111-47FB-A32E-E5214BB172BE}" name="Tabella4" displayName="Tabella4" ref="A1:G57" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68">
-  <autoFilter ref="A1:G57" xr:uid="{AD0662AD-6111-47FB-A32E-E5214BB172BE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{AD0662AD-6111-47FB-A32E-E5214BB172BE}" name="Tabella4" displayName="Tabella4" ref="A1:G58" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68">
+  <autoFilter ref="A1:G58" xr:uid="{AD0662AD-6111-47FB-A32E-E5214BB172BE}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6899A739-52B8-45B2-B22F-D77E240FA270}" name="Nome Carta" dataDxfId="66"/>
     <tableColumn id="2" xr3:uid="{F5DF84CC-A246-40FD-980E-E7E55E602B3A}" name="Tipo" dataDxfId="65"/>
@@ -11166,7 +11172,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -12225,7 +12231,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>167</v>
@@ -12282,7 +12288,7 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>167</v>
@@ -12290,7 +12296,7 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>15</v>
@@ -12301,7 +12307,7 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>167</v>
@@ -12309,7 +12315,7 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>15</v>
@@ -12320,7 +12326,7 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>167</v>
@@ -12328,7 +12334,7 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>15</v>
@@ -12339,7 +12345,7 @@
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>167</v>
@@ -12347,7 +12353,7 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>15</v>
@@ -12358,955 +12364,35 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="8">
+        <v>25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>10</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194294E8-D762-4C6A-93FD-65E9EBEA6F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A5464C-CE41-4223-B4F5-E83F3AAD71ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,9 +924,6 @@
     <t>Finche questa carta è presente sul terreno, i tuoi Santi sono immuni agli effetti delle maledizioni.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni volta che un Token o un Santo viene mandato dal campo al cimitero, questo santo riceve +1 Fede e +1 Forza.</t>
-  </si>
-  <si>
     <t>Se questo Santo viene sconfitto da un Santo avversario, puoi prendere ogni carta "Pietra" dal tuo cimitero e metterla nel tuo reliquiario. Poi mischia il reliquiario. Se attivi questo effetto, scomunica questa carta.</t>
   </si>
   <si>
@@ -942,42 +939,24 @@
     <t>Ogni volta che questo Santo subisce danno non mortale, riceve +7 Fede.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni volta che un tuo Santo viene distrutto o giochi una carta "Sigillo", aggiungi 1 Segnalino Sigillo su questa carta. Puoi rimuovere un numero di Segnalini Sigillo pari alle Croci di una carta (tua o avversaria) il cui effetto sta per distruggere questa carta: annulla quell'effetto e questa carta non viene distrutta. Quando questa carta lascia il campo, rimuovi tutti i Segnalini Sigillo presenti su di essa.</t>
-  </si>
-  <si>
     <t>Quando questo Santo attacca un Santo avversario, dopo il calcolo del danno, equipaggia questa carta a quel Santo. Alla fine del prossimo turno, distruggi il Santo equipaggiato e scomunica questa carta.</t>
   </si>
   <si>
     <t>Quando questa carta lascia il campo, evoca un Token Spirito Vacuo sul tuo campo.</t>
   </si>
   <si>
-    <t>Puoi mandare questa carta dal campo al cimitero: evoca un qualsiasi Santo bersaglio dal tuo cimitero in zona d'attacco.</t>
-  </si>
-  <si>
-    <t>Se questo Santo distrugge un Santo con un attacco, torna nella tua mano. L'effetto di questa carta può essere attivato una volta per turno.</t>
-  </si>
-  <si>
     <t>Se Altare dei Sette Sigilli è sul campo con almeno 7 Segnalini Sigillo, questo Santo riceve +5 Forza. Quando questo Santo viene sconfitto in battaglia o distrutto per effetto di una carta, aggiungi 3 Segnalini Sigillo su Altare dei Sette Sigilli.</t>
   </si>
   <si>
     <t>Scegli due Santi sul campo. Distruggi tutti gli altri Santi.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ricevi +1 Ispirazione in questo turno.</t>
-  </si>
-  <si>
     <t>Scegli una carta Santo dal tuo cimitero e aggiungila alla tua mano.</t>
   </si>
   <si>
     <t>Gioca questa carta solo se 3 o più tuoi Santi sono stati mandati dalla tua mano o dal campo al cimitero in questo turno. Evoca "Fenrir" o "Jormungandr" dal tuo reliquiario o cimitero sul tuo campo.</t>
   </si>
   <si>
-    <t>Puoi giocare questa carta senza pagare il suo costo di Ispirazione. Finche questa carta è sul terreno, puoi giocare i Santi dalla tua mano pagando metà del loro costo di Ispirazione (arrotondato per eccesso).</t>
-  </si>
-  <si>
-    <t>Finche questo edificio è sul terreno, ogni volta che l'avversario pesca una carta, questa carta perde 1 Fede e rimuovi 2 Peccato da te stesso. Se la Fede di questa carta diventa 0, distruggi Av'drna.</t>
-  </si>
-  <si>
     <t>Ogni giocatore pesca 3 carte.</t>
   </si>
   <si>
@@ -990,18 +969,9 @@
     <t>Equipaggia questa carta a un Santo bersaglio. Quando la Fede di quel Santo diventa 0, puoi distruggere questa carta: quel Santo rimane con 1 Fede invece di essere sconfitto.</t>
   </si>
   <si>
-    <t>Finche questo edificio è sul tuo terreno, ogni volta che giochi una Benedizione o una Maledizione, aggiungi 1 Segnalino su questa carta. Puoi rimuovere 3 Segnalini da questa carta: cerca nel tuo reliquiario una Benedizione o Maledizione, rivelala e aggiungila alla tua mano. Poi mischia il reliquiario.</t>
-  </si>
-  <si>
-    <t>Finche questo edificio è sul tuo terreno, ogni volta che giochi una Benedizione, pesca una carta. Se è un Santo, scomunica quella carta. Se è un Artefatto o Edificio, rimetti quella carta nel tuo reliquiario e mischia. Se è una Benedizione o Maledizione, tienila in mano.</t>
-  </si>
-  <si>
     <t>Scomunica un Santo bersaglio, poi infliggi Peccato all'avversario pari alla Fede di quel Santo.</t>
   </si>
   <si>
-    <t>Per giocare questa carta, scegli un santo bersaglio sul tuo terreno e distruggilo. Successivamente, aggiungi la Fede iniziale del Santo sacrificato alla Fede di questa carta. Quando questo Santo viene sconfitto in battaglia o distrutto per effetto di una carta non genera Peccato.</t>
-  </si>
-  <si>
     <t>All'inizio del tuo turno, paga 5 Peccato, altrimenti distruggi questa carta. Alla fine del tuo turno, distruggi ogni tuo Token Spirito Vacuo. L'avversario riceve 5 Peccato per ogni Token distrutto in questo modo.</t>
   </si>
   <si>
@@ -1011,21 +981,6 @@
     <t>Mentre Campana è sul tuo terreno, all'inizio del tuo turno, aggiungi su di essa 1 Segnalino. Puoi attivare l'effetto di questa carta rimuovendo un qualsiasi numero di Segnalini da essa. Il costo in Ispirazione per attivare questo effetto è pari al numero di Segnalini rimossi. Per ogni Segnalino rimosso, ogni tuo Santo sul campo riceve +1 Fede.</t>
   </si>
   <si>
-    <t>Finche quesa carta è sul terreno, una volta per turno, scegli uno dei seguenti effetti: • Prendi un Santo dal tuo cimitero e aggiungilo alla tua mano, poi distruggi questa carta. • Se non controlli Santi, annulla il primo attacco che ricevi durante il prossimo turno avversario.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, prima della tua fase di pescata, devi distruggere un Santo bersaglio sul campo. Se hai distrutto un tuo Santo, infliggi 2 Peccato all'avversario. Se hai distrutto un Santo avversario, rimuovi 1 Peccato. Se, durante l'attivazione di questo effetto non sono presenti santi sul terreno, distruggi questa carta.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, ogni carta "Pietra" distrutta viene messa nel reliquiario del suo proprietario invece che nel cimitero.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, una volta per turno, puoi distruggere un tuo Santo bersaglio. Rimuovi Peccato pari alla Fede di quel Santo al momento della distruzione.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, ogni volta che peschi una carta, ogni tuo Santo sul campo riceve +2 Fede.</t>
-  </si>
-  <si>
     <t>Una volta per turno, scegli una carta Santo con Croci pari o inferiori a 4 nel tuo cimitero. Evoca quel Santo sul tuo campo senza pagare il suo costo di Ispirazione.</t>
   </si>
   <si>
@@ -1056,9 +1011,6 @@
     <t>Manda tutte le carte dalla tua mano al cimitero. Poi pesca 5 carte.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni volta che un Token Albero viene sconfitto, infliggi 1 Peccato all'avversario.</t>
-  </si>
-  <si>
     <t>Tre tuoi Santi bersaglio ricevono +5 Fede ciascuno.</t>
   </si>
   <si>
@@ -1068,9 +1020,6 @@
     <t>Per giocare questa carta, devi scomunicare dal tuo cimitero una copia di "Giorno 1", "Giorno 2", "Giorno 3", "Giorno 4", "Giorno 5", "Giorno 6" e "Giorno 7". Questa carta non può essere bersagliata da effetti.</t>
   </si>
   <si>
-    <t>Quando questo santo entra in campo, guarda la prima carta del tuo reliquiario. Se è una Benedizione o Maledizione, pescala. Altrimenti, rimischia il reliquiario.</t>
-  </si>
-  <si>
     <t>Cerca fino a 3 carte Albero nel tuo reliquiario e mandale al cimitero.</t>
   </si>
   <si>
@@ -1083,39 +1032,18 @@
     <t>Puoi pescare fino a 5 carte. Ogni carta pescata in questo modo costa 2 Ispirazione in questo turno.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni volta che un tuo Santo viene mandato al cimitero, evoca un Token Spirito Vacuo sul suo posto.</t>
-  </si>
-  <si>
     <t>Prendi il controllo di un tuo Santo e spostalo sul campo dell'avversario fino alla fine del turno. Quando quel Santo viene sconfitto, il giocatore che lo controlla in quel momento riceve Peccato pari alla sua Fede iniziale.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, durante la tua fase di pescata, pesca una carta aggiuntiva.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, una volta per turno, quando l'avversario pesca una carta, puoi fargli rimischiare quella carta nel reliquiario e pescare di nuovo.</t>
-  </si>
-  <si>
     <t>Ogni volta che questo Santo dichiara un attacco ad un Santo avversario, prima del calcolo del danno, riceve +1 Forza.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni volta che un Santo avversario attacca, subisce 2 danni. Se un Santo avversario viene distrutto da questo effetto, rimuovi 2 Peccato.</t>
-  </si>
-  <si>
     <t>Un Santo bersaglio riceve +3 Forza. Se controlli Odino, quel Santo riceve +6 Forza invece. Se controlli Odino e Thor, quel Santo riceve +6 Forza e peschi una carta.</t>
   </si>
   <si>
     <t>Ogni Santo con espansione "Animismo" sul tuo campo riceve +2 Fede e +2 Forza.</t>
   </si>
   <si>
-    <t>Finche questa carta è sul terreno, ogni carta che passa dal tuo campo direttamente al cimitero viene invece aggiunta alla tua mano.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, le tue carte Albero non possono essere bersagliate da Maledizioni o Benedizioni avversarie. Se una carta Albero viene scomunicata, viene messa nel reliquiario del suo proprietario invece che nella zona scomunicate.</t>
-  </si>
-  <si>
-    <t>Finche questa carta è sul terreno, una volta per turno puoi scomunicare la carta in cima al tuo reliquiario.</t>
-  </si>
-  <si>
     <t>Fino a quando questo Santo è sul campo, ogni volta che l'avversario pesca una carta, ogni tuo Santo sul campo riceve +1 Fede.</t>
   </si>
   <si>
@@ -1143,9 +1071,6 @@
     <t>I Santi avversari con Croci pari o inferiori a 2 non possono attaccare.</t>
   </si>
   <si>
-    <t>Rendi inutilizzabile uno slot Artefatto dell'avversario a tua scelta.</t>
-  </si>
-  <si>
     <t>Puoi giocare una carta Artefatto dalla tua mano pagando metà del suo costo di Ispirazione (arrotondato per eccesso).</t>
   </si>
   <si>
@@ -1173,9 +1098,6 @@
     <t>Prendi tutte le carte da tutti i cimiteri e rimettile nei rispettivi reliquiari. Poi ogni giocatore mischia il proprio reliquiario.</t>
   </si>
   <si>
-    <t>Se questo Santo distrugge un Santo avversario, aumenta la sua Fede a 4.</t>
-  </si>
-  <si>
     <t>Quando questa carta entra in campo, puoi evocare un Token Gub-ner sul tuo campo. Ogni volta che un Token Gub-ner viene sconfitto, puoi scegliere una carta scomunicata e rimetterla nel reliquiario del suo proprietario. Poi mischia.</t>
   </si>
   <si>
@@ -1188,9 +1110,6 @@
     <t>Quando giochi questo santo mentre Odino è presente sul tuo terreno, guarda le prime 3 carte del tuo reliquiario. Puoi aggiungere una qualsiasi di quelle carte alla tua mano e successivamente mischiare il reliquiario.</t>
   </si>
   <si>
-    <t>Per ogni 5 carte nel tuo cimitero, questa carta riceve +2 Fede e +2 Forza.</t>
-  </si>
-  <si>
     <t>Se non controlli altri Santi, puoi giocare questa carta senza pagare il suo costo di Ispirazione.</t>
   </si>
   <si>
@@ -1623,9 +1542,6 @@
     <t>Guarda la carta in fondo al tuo reliquiario. Puoi spostarla in cima o lasciarla in fondo.</t>
   </si>
   <si>
-    <t>Puoi includere questa carta solo in un reliquiario composto interamente da carte con espansione Ph-Dak'Gaph. Ogni volta che un giocatore pesca una carta riceve 1 peccato. Ogni volta che una carta viene scomunicata, perdi 1 peccato.</t>
-  </si>
-  <si>
     <t>Distruggi un Santo sul terreno dell'avversario.</t>
   </si>
   <si>
@@ -1647,9 +1563,6 @@
     <t>Questa carta può essere evocata solo tramite "Specchio di Ykknødar". Non può essere distrutta da effetti. Non può attaccare. Ogni volta che l'avversario pesca una carta, rimuovi 3 Peccato.</t>
   </si>
   <si>
-    <t>Manda una santo bersaglio dal tuo deck al cimitero. Rimuovi peccato pari alla fede e forza di quel santo.</t>
-  </si>
-  <si>
     <t>Cerca un artefatto nel tuo reliquiario o cimitero e posizionalo sul terreno senza pagare ispirazione.</t>
   </si>
   <si>
@@ -1659,39 +1572,15 @@
     <t>Una volta per turno, puoi distruggere un Token Gub-ner sul tuo terreno. Se lo fai, seleziona e distruggi una carta sul terreno avversario.</t>
   </si>
   <si>
-    <t>Equipaggia questa carta ad una tua carta edificio. Quando quella carta verrebbe distrutta per effetto di una carta, imposta la sua fede a 10 e scomunica questa carta.</t>
-  </si>
-  <si>
-    <t>Ogni volta che un Token Gub-ner viene evocato sul tuo terreno, distruggilo immediatamente. Per ogni Token Gub-ner distrutto tramite questo effetto, scomunica la prima carta del tuo reliquiario e perdi 3 peccato.</t>
-  </si>
-  <si>
-    <t>Ogni volta che una tua carta viene scomunicata, il tuo avversario riceve 3 peccato.</t>
-  </si>
-  <si>
-    <t>Quando questo santo viene sconfitto o distrutto, scomunicalo. Quando questa carta viene scomunicata puoi prendere fino a 3 carte dalla tua mano e rimetterle nel reliquiario.Poi, pescane altrettante.</t>
-  </si>
-  <si>
-    <t>Dopo il calcolo dei danni, Infliggi gli stessi danni che questa carta riceve al santo avversario attaccante. Se quel santo viene distrutto tramite questo effetto, perdi peccato pari alla fede iniziale di quel santo.</t>
-  </si>
-  <si>
     <t>Cerca nel tuo reliquiario un artefatto. Giocalo sul tuo terreno e scomunica questa carta.</t>
   </si>
   <si>
     <t>Manda una tua carta dalla mano al cimitero. Pesca 3 carte.</t>
   </si>
   <si>
-    <t>Un tuo Santo bersaglio riceve +7 Fede.</t>
-  </si>
-  <si>
-    <t>Due tuoi Santi bersaglio ricevono +6 Fede ciascuno.</t>
-  </si>
-  <si>
     <t>Un tuo Santo bersaglio riceve Fede pari alla sua fede iniziale.</t>
   </si>
   <si>
-    <t>Gioca questa carta solo se il Peccato dell'avversario è pari o inferiore a 50. L'avversario riceve 10 Peccato.</t>
-  </si>
-  <si>
     <t>Assalto</t>
   </si>
   <si>
@@ -1740,9 +1629,6 @@
     <t>Recupero da Cimitero</t>
   </si>
   <si>
-    <t>Scegli fino a 3 carte scomunicate bersaglio, rimettile nel tuo reliquiario e mischialo. Successivamente, se controlli Av'drna o Ph'drna, pesca una carta.</t>
-  </si>
-  <si>
     <t>1/4 (-3)</t>
   </si>
   <si>
@@ -1812,27 +1698,15 @@
     <t>Editto del Faraone</t>
   </si>
   <si>
-    <t>Scegli un artefatto o un edificio avversario. Distruggilo. Poi, ricevi 3 peccato.</t>
-  </si>
-  <si>
     <t>Offerta al Nilo</t>
   </si>
   <si>
-    <t>Manda 1 carta dalla mano al cimitero; pesca 2 carte. Se la carta mandata era un santo, rimuovi 3 peccato.</t>
-  </si>
-  <si>
     <t>Rito di Imbalsamazione Regale</t>
   </si>
   <si>
-    <t>Scegli 1 santo nel tuo cimitero con croci inferiori o uguali a 6; aggiungilo alla mano. Poi, puoi mandare una carta dalla mano al cimitero.</t>
-  </si>
-  <si>
     <t>Guardia del Sarcofago</t>
   </si>
   <si>
-    <t>Una volta per turno, quando subiresti il primo attacco dietto, annullalo. Poi questa carta perte 2 fede. Quando la fede di questa carta diventa pari o inferiore a 0, distrggila.</t>
-  </si>
-  <si>
     <t>Via della Piramide</t>
   </si>
   <si>
@@ -1842,67 +1716,193 @@
     <t>Piaga: Acque di Sangue</t>
   </si>
   <si>
-    <t>Ogni Santo avversario perde 2 Fede. Poi puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario.</t>
-  </si>
-  <si>
     <t>Piaga: Rane Invasive</t>
   </si>
   <si>
-    <t>Infliggi 6 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Piaga delle Locuste</t>
   </si>
   <si>
     <t>Piaga: Tenebre d'Egitto</t>
   </si>
   <si>
-    <t>Durante il prossimo turno dell'avversario, pesca 1 carta in meno (minimo 1). Cerca nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario.</t>
-  </si>
-  <si>
     <t>Piaga: Morte dei Primogeniti</t>
   </si>
   <si>
-    <t>Un Santo avversario perde 6 Fede. Poi infliggi 4 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Piaga: Zanzare del Deserto</t>
   </si>
   <si>
     <t>Piaga: Mosche d'Egitto</t>
   </si>
   <si>
-    <t>Scegli 1 Artefatto o 1 Edificio avversario: distruggilo. Poi puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario.</t>
-  </si>
-  <si>
     <t>Piaga: Ulcere della Carne</t>
   </si>
   <si>
     <t>Piaga: Grandine di Fuoco</t>
   </si>
   <si>
-    <t>Ogni Santo avversario perde 3 Fede. Poi puoi distruggere 1 Artefatto avversario. Poi puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario.</t>
-  </si>
-  <si>
     <t>Piaga: Morte del Bestiame</t>
   </si>
   <si>
-    <t>Scegli un santo sul terreno e distruggilo. Poi infliggi 3 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Una volta per turno, quando questa carta attacca un Santo avversario, puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
   </si>
   <si>
     <t>Portatore delle Piaghe</t>
   </si>
   <si>
-    <t>Ogni Santo avversario perde 3 Fede. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
-    <t>Scegli fino a 2 Santi avversari: ognuno perde 4 Fede. Poi infliggi 2 Peccato all'avversario. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
-  </si>
-  <si>
     <t>Questa carta può essere evocata solo scomunicando 3 carte Piaga dalla tua mano o cimitero, senza pagare costo di Ispirazione. Questa carta non può essere bersagliata dagli effetti di altre carte. Una volta per turno, scegli e attiva un effetto di qualsiasi carta "Piaga" benedizione o maledizione.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un tuo Santo viene distrutto o giochi una carta "Sigillo", aggiungi 1 Segnalino Sigillo su questa carta. Puoi rimuovere un numero di Segnalini Sigillo pari alle Croci di una carta (tua o avversaria) il cui effetto sta per distruggere questa carta: annulla quell'effetto e questa carta non viene distrutta. Quando questa carta lascia il campo, rimuovi tutti i Segnalini Sigillo.</t>
+  </si>
+  <si>
+    <t>All'inizio del tuo turno, ricevi +1 Ispirazione in questo turno.</t>
+  </si>
+  <si>
+    <t>Ogni volta che giochi una Benedizione o una Maledizione, aggiungi 1 Segnalino su questa carta. Puoi rimuovere 3 Segnalini da questa carta: cerca nel tuo reliquiario una Benedizione o Maledizione, rivelala e aggiungila alla tua mano. Poi mischia il reliquiario.</t>
+  </si>
+  <si>
+    <t>Ogni volta che giochi una Benedizione, pesca una carta. Se è un Santo, scomunica quella carta. Se è un Artefatto o Edificio, rimetti quella carta nel tuo reliquiario e mischia. Se è una Benedizione o Maledizione, tienila in mano.</t>
+  </si>
+  <si>
+    <t>Sacrifica un tuo Santo. Quando giochi questa carta, aggiungi la Fede iniziale del Santo sacrificato alla Fede di questa carta. Quando questo Santo viene sconfitto in battaglia o distrutto per effetto di una carta non genera Peccato.</t>
+  </si>
+  <si>
+    <t>Una volta per turno, scegli uno dei seguenti effetti: � Prendi un Santo dal tuo cimitero e aggiungilo alla tua mano, poi distruggi questa carta. � Se non controlli Santi, annulla il primo attacco che ricevi durante il prossimo turno avversario.</t>
+  </si>
+  <si>
+    <t>Ogni volta che peschi una carta, ogni tuo Santo sul campo riceve +2 Fede.</t>
+  </si>
+  <si>
+    <t>Se questo Santo distrugge un Santo con un attacco, torna nella tua mano.</t>
+  </si>
+  <si>
+    <t>Prima della tua fase di pescata, devi distruggere un Santo bersaglio sul campo. Se hai distrutto un tuo Santo, infliggi 2 Peccato all'avversario. Se hai distrutto un Santo avversario, rimuovi 1 Peccato. Se, durante l'attivazione di questo effetto non sono presenti santi sul terreno, distruggi questa carta.</t>
+  </si>
+  <si>
+    <t>Ogni carta "Pietra" distrutta viene messa nel reliquiario del suo proprietario invece che nel cimitero.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un Token Albero viene sconfitto, infliggi 1 Peccato all'avversario.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un Santo avversario attacca, subisce 2 danni. Se un Santo avversario viene distrutto da questo effetto, rimuovi 2 Peccato.</t>
+  </si>
+  <si>
+    <t>Le tue carte Albero non possono essere bersagliate da Maledizioni o Benedizioni avversarie. Se una carta Albero viene scomunicata, viene messa nel reliquiario del suo proprietario invece che nella zona scomunicate.</t>
+  </si>
+  <si>
+    <t>Se questo Santo distrugge un Santo avversario, aumenta la sua Fede di 4.</t>
+  </si>
+  <si>
+    <t>Puoi mandare questa carta dal campo al cimitero: evoca un qualsiasi Santo bersaglio dal tuo cimitero.</t>
+  </si>
+  <si>
+    <t>Puoi giocare questa carta senza pagare il suo costo di Ispirazione. Puoi giocare i Santi dalla tua mano pagando metà del loro costo di Ispirazione (arrotondato per eccesso).</t>
+  </si>
+  <si>
+    <t>Guarda la prima carta del tuo reliquiario. Se è una Benedizione o Maledizione, pescala. Altrimenti, rimischia il reliquiario.</t>
+  </si>
+  <si>
+    <t>Durante la tua fase di pescata, pesca una carta aggiuntiva.</t>
+  </si>
+  <si>
+    <t>Una volta per turno, quando l'avversario pesca una carta, puoi fargli rimischiare quella carta nel reliquiario e pescare di nuovo.</t>
+  </si>
+  <si>
+    <t>Manda un Santo bersaglio dal tuo reliquiario al cimitero. Rimuovi Peccato pari alla Fede e Forza di quel Santo.</t>
+  </si>
+  <si>
+    <t>Scegli 1 Artefatto o 1 Edificio avversario. Distruggilo. Poi ricevi 3 Peccato.</t>
+  </si>
+  <si>
+    <t>Manda 1 carta dalla mano al cimitero; pesca 2 carte. Se la carta mandata era un Santo, rimuovi 3 Peccato.</t>
+  </si>
+  <si>
+    <t>Scegli 1 tuo Santo nel cimitero con Croci pari o inferiori a 6: aggiungilo alla mano. Poi puoi mandare 1 carta dalla tua mano al cimitero.</t>
+  </si>
+  <si>
+    <t>Una volta per turno, quando subiresti il primo attacco diretto, annullalo. Poi questa carta perde 2 Fede. Quando la Fede di questa carta diventa pari o inferiore a 0, distruggila.</t>
+  </si>
+  <si>
+    <t>Ogni volta che l'avversario pesca una carta, questa carta perde 1 Fede e tu rimuovi 2 Peccato. Se la Fede di questa carta diventa 0, distruggi Av'drna.</t>
+  </si>
+  <si>
+    <t>Una volta per turno, puoi attivare l'effetto di questa carta: scomunica la carta in cima al tuo reliquiario.</t>
+  </si>
+  <si>
+    <t>Quando questa carta entra in campo, scegli uno slot Artefatto avversario: quello slot diventa inutilizzabile finche questa carta rimane sul terreno.</t>
+  </si>
+  <si>
+    <t>Scegli fino a 3 carte scomunicate bersaglio, rimettile nel tuo reliquiario e mischialo.Successivamente, se controlli Av'drna o Ph'drna, pesca una carta.</t>
+  </si>
+  <si>
+    <t>Puoi includere questa carta solo in un reliquiario composto interamente da carte con espansione Ph-Dak'Gaph. Ogni volta che peschi una carta, ricevi 1 Peccato. Ogni volta che una carta viene scomunicata, rimuovi 1 Peccato.</t>
+  </si>
+  <si>
+    <t>Equipaggia questa carta a un tuo Edificio. Quando quell'Edificio verrebbe distrutto per effetto di una carta, imposta la sua Fede a 10 e scomunica questa carta.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un Token Gub-ner viene evocato sul tuo terreno, distruggilo immediatamente. Per ogni Token Gub-ner distrutto tramite questo effetto, scomunica la prima carta del tuo reliquiario e rimuovi 3 Peccato.</t>
+  </si>
+  <si>
+    <t>Ogni volta che una tua carta viene scomunicata, il tuo avversario riceve 3 Peccato.</t>
+  </si>
+  <si>
+    <t>Quando questo Santo viene sconfitto o distrutto, scomunicalo. Quando questa carta viene scomunicata, puoi prendere fino a 3 carte dalla tua mano e rimetterle nel reliquiario. Poi, pescane altrettante.</t>
+  </si>
+  <si>
+    <t>Quando questa carta riceve danno da un Santo avversario, quel Santo subisce lo stesso danno. Se quel Santo viene distrutto da questo effetto, rimuovi Peccato pari alla sua Fede iniziale.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un Token o un Santo viene mandato dal campo al cimitero, questo santo riceve +1 Fede e +1 Forza.</t>
+  </si>
+  <si>
+    <t>Una volta per turno, puoi distruggere un tuo Santo bersaglio. Rimuovi Peccato pari alla Fede di quel Santo al momento della distruzione.</t>
+  </si>
+  <si>
+    <t>Ogni volta che un tuo Santo viene mandato al cimitero, evoca un Token Spirito Vacuo sul suo posto.</t>
+  </si>
+  <si>
+    <t>Ogni carta che passa dal tuo campo direttamente al cimitero viene invece aggiunta alla tua mano.</t>
+  </si>
+  <si>
+    <t>Quando questo Santo scende in campo, per ogni 5 carte nel tuo cimitero questa carta riceve +2 Fede e +2 Forza.</t>
+  </si>
+  <si>
+    <t>Un tuo Santo bersaglio riceve +5 Fede.</t>
+  </si>
+  <si>
+    <t>Due tuoi Santi bersaglio ricevono +3 Fede ciascuno.</t>
+  </si>
+  <si>
+    <t>Gioca questa carta solo se il Peccato dell'avversario è pari o inferiore a 50. L'avversario riceve 15 Peccato.</t>
+  </si>
+  <si>
+    <t>Ogni Santo avversario perde 2 Fede. Puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario. Infine infliggi 1 Peccato a te stesso.</t>
+  </si>
+  <si>
+    <t>Infliggi 6 Peccato all'avversario e 1 a te stesso. Puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Durante il prossimo turno dell'avversario, pesca 1 carta in meno (minimo 1). Cerca nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario. Infine infliggi 1 Peccato a te stesso.</t>
+  </si>
+  <si>
+    <t>Un Santo avversario perde 6 Fede. Infliggi 4 Peccato all'avversario e 1 a te stesso. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Ogni Santo avversario perde 3 Fede. Poi puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano. Infine, infliggi 1 Peccato a te stesso.</t>
+  </si>
+  <si>
+    <t>Scegli 1 Artefatto o 1 Edificio avversario: distruggilo. Poi puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario. Infine infliggi 2 Peccato a te stesso.</t>
+  </si>
+  <si>
+    <t>Scegli fino a 2 Santi avversari: ognuno perde 4 Fede. Poi infliggi 3 Peccato all'avversario e 1 a te stesso. Puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
+  </si>
+  <si>
+    <t>Ogni Santo avversario perde 3 Fede. Poi puoi distruggere 1 Artefatto avversario. Puoi cercare nel tuo reliquiario una carta "Piaga", aggiungerla alla tua mano e mischiare il reliquiario. Infine infliggi 2 Peccato a te stesso.</t>
+  </si>
+  <si>
+    <t>Scegli un santo sul terreno e distruggilo. Poi infliggi 3 Peccato all'avversario e 2 a te stesso. Puoi riprendere dal tuo cimitero una carta "Piaga" e aggiungerla alla tua mano.</t>
   </si>
 </sst>
 </file>
@@ -3676,28 +3676,28 @@
         <v>6</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>557</v>
+        <v>520</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>558</v>
+        <v>521</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>559</v>
+        <v>522</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>560</v>
+        <v>523</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>563</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3705,28 +3705,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>567</v>
+        <v>529</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>568</v>
+        <v>530</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>569</v>
+        <v>531</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>571</v>
+        <v>533</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>572</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3734,28 +3734,28 @@
         <v>103</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>573</v>
+        <v>535</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>567</v>
+        <v>529</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>575</v>
+        <v>537</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>571</v>
+        <v>533</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3763,28 +3763,28 @@
         <v>167</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>578</v>
+        <v>540</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>568</v>
+        <v>530</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3792,28 +3792,28 @@
         <v>209</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>579</v>
+        <v>541</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>583</v>
+        <v>545</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3821,28 +3821,28 @@
         <v>246</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>584</v>
+        <v>546</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>568</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3850,28 +3850,28 @@
         <v>78</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>585</v>
+        <v>547</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>586</v>
+        <v>548</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>565</v>
+        <v>527</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" x14ac:dyDescent="0.25">
@@ -3879,28 +3879,28 @@
         <v>271</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>566</v>
+        <v>528</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>585</v>
+        <v>547</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>574</v>
+        <v>536</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>577</v>
+        <v>539</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>576</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>298</v>
+        <v>568</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>9</v>
@@ -4008,7 +4008,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>9</v>
@@ -4027,7 +4027,7 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>9</v>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>305</v>
+        <v>569</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>9</v>
@@ -4067,7 +4067,7 @@
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>9</v>
@@ -4088,13 +4088,13 @@
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>314</v>
+        <v>570</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
@@ -4109,13 +4109,13 @@
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>315</v>
+        <v>571</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>317</v>
+        <v>572</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>9</v>
@@ -4153,13 +4153,13 @@
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>321</v>
+        <v>573</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>9</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>325</v>
+        <v>574</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>9</v>
@@ -4214,7 +4214,7 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>9</v>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>9</v>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>9</v>
@@ -4283,7 +4283,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>9</v>
@@ -4302,7 +4302,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>9</v>
@@ -4325,7 +4325,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>9</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>9</v>
@@ -4365,7 +4365,7 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>9</v>
@@ -4384,7 +4384,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>9</v>
@@ -4403,7 +4403,7 @@
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>9</v>
@@ -4422,7 +4422,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>9</v>
@@ -4441,7 +4441,7 @@
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>9</v>
@@ -4464,7 +4464,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>9</v>
@@ -4487,7 +4487,7 @@
         <v>3</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>9</v>
@@ -4506,7 +4506,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>9</v>
@@ -4525,7 +4525,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="12" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>9</v>
@@ -4544,7 +4544,7 @@
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>9</v>
@@ -4567,7 +4567,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>9</v>
@@ -4590,7 +4590,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>9</v>
@@ -4613,7 +4613,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>9</v>
@@ -4632,7 +4632,7 @@
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>403</v>
+        <v>376</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>9</v>
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>405</v>
+        <v>378</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>9</v>
@@ -4678,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>9</v>
@@ -4697,7 +4697,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>9</v>
@@ -4720,7 +4720,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>9</v>
@@ -4743,7 +4743,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>9</v>
@@ -4766,7 +4766,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>9</v>
@@ -4785,7 +4785,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>9</v>
@@ -4804,7 +4804,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>427</v>
+        <v>400</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>9</v>
@@ -4823,7 +4823,7 @@
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>444</v>
+        <v>417</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>9</v>
@@ -4846,7 +4846,7 @@
         <v>3</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>446</v>
+        <v>419</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>9</v>
@@ -4865,7 +4865,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>9</v>
@@ -4884,7 +4884,7 @@
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>9</v>
@@ -4907,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>9</v>
@@ -4926,7 +4926,7 @@
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>9</v>
@@ -4945,7 +4945,7 @@
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="12" t="s">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>9</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E50" s="14"/>
       <c r="F50" s="12" t="s">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>9</v>
@@ -4985,7 +4985,7 @@
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>472</v>
+        <v>445</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>9</v>
@@ -5004,7 +5004,7 @@
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>9</v>
@@ -5023,7 +5023,7 @@
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>9</v>
@@ -5042,7 +5042,7 @@
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>9</v>
@@ -5061,7 +5061,7 @@
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="12" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>9</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="12" t="s">
-        <v>503</v>
+        <v>476</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>9</v>
@@ -5101,7 +5101,7 @@
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>9</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="12" t="s">
-        <v>512</v>
+        <v>485</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>9</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>514</v>
+        <v>487</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>9</v>
@@ -5166,7 +5166,7 @@
         <v>3</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>519</v>
+        <v>492</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>9</v>
@@ -5185,7 +5185,7 @@
       <c r="D61" s="14"/>
       <c r="E61" s="14"/>
       <c r="F61" s="12" t="s">
-        <v>520</v>
+        <v>493</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>9</v>
@@ -5208,7 +5208,7 @@
         <v>5</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>9</v>
@@ -5231,7 +5231,7 @@
         <v>4</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>522</v>
+        <v>495</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>9</v>
@@ -5250,7 +5250,7 @@
       <c r="D64" s="14"/>
       <c r="E64" s="14"/>
       <c r="F64" s="12" t="s">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>9</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="65" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>18</v>
@@ -5269,13 +5269,13 @@
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
       <c r="F65" s="12" t="s">
-        <v>551</v>
+        <v>514</v>
       </c>
       <c r="G65" s="7"/>
     </row>
     <row r="66" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>18</v>
@@ -5286,13 +5286,13 @@
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="12" t="s">
-        <v>553</v>
+        <v>516</v>
       </c>
       <c r="G66" s="7"/>
     </row>
     <row r="67" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>554</v>
+        <v>517</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>18</v>
@@ -5303,7 +5303,7 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="12" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="G67" s="7"/>
     </row>
@@ -7372,7 +7372,7 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="16" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>78</v>
@@ -7391,7 +7391,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>78</v>
@@ -7414,7 +7414,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>78</v>
@@ -7433,7 +7433,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>78</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>78</v>
@@ -7477,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>78</v>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>78</v>
@@ -7521,7 +7521,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>78</v>
@@ -7544,7 +7544,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>78</v>
@@ -7567,7 +7567,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>396</v>
+        <v>369</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>78</v>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="16" t="s">
-        <v>402</v>
+        <v>375</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>78</v>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>78</v>
@@ -7632,7 +7632,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>78</v>
@@ -7655,7 +7655,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>78</v>
@@ -7674,7 +7674,7 @@
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>78</v>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>78</v>
@@ -7718,7 +7718,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>78</v>
@@ -7741,7 +7741,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>78</v>
@@ -7764,7 +7764,7 @@
         <v>3</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>78</v>
@@ -7787,7 +7787,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>78</v>
@@ -7806,7 +7806,7 @@
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16" t="s">
-        <v>501</v>
+        <v>474</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>78</v>
@@ -7829,7 +7829,7 @@
         <v>8</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>78</v>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="16" t="s">
-        <v>517</v>
+        <v>490</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>78</v>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="12" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>78</v>
@@ -8982,7 +8982,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>103</v>
@@ -9005,7 +9005,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>103</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>103</v>
@@ -9051,7 +9051,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>103</v>
@@ -9074,7 +9074,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>103</v>
@@ -9097,7 +9097,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>103</v>
@@ -9120,7 +9120,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>302</v>
+        <v>575</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>103</v>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>322</v>
+        <v>576</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>103</v>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>323</v>
+        <v>577</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>103</v>
@@ -9179,7 +9179,7 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>103</v>
@@ -9198,7 +9198,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>103</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>103</v>
@@ -9242,7 +9242,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>103</v>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>336</v>
+        <v>578</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>103</v>
@@ -9282,7 +9282,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>103</v>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>350</v>
+        <v>579</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>103</v>
@@ -9322,13 +9322,13 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>121</v>
       </c>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>354</v>
+        <v>580</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>103</v>
@@ -9366,7 +9366,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>375</v>
+        <v>581</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>103</v>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>103</v>
@@ -9410,7 +9410,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>103</v>
@@ -9433,7 +9433,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>103</v>
@@ -9452,7 +9452,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>103</v>
@@ -9475,7 +9475,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>103</v>
@@ -9494,7 +9494,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>103</v>
@@ -9513,7 +9513,7 @@
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>404</v>
+        <v>377</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>103</v>
@@ -9532,7 +9532,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>103</v>
@@ -9555,7 +9555,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>103</v>
@@ -9578,7 +9578,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>103</v>
@@ -9601,7 +9601,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>103</v>
@@ -9620,7 +9620,7 @@
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="12" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>103</v>
@@ -9643,7 +9643,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>103</v>
@@ -9666,7 +9666,7 @@
         <v>6</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>103</v>
@@ -9685,7 +9685,7 @@
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>103</v>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>103</v>
@@ -9725,7 +9725,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>103</v>
@@ -9744,7 +9744,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="12" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>103</v>
@@ -9763,7 +9763,7 @@
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>439</v>
+        <v>412</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>103</v>
@@ -9782,7 +9782,7 @@
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="12" t="s">
-        <v>445</v>
+        <v>418</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>103</v>
@@ -9801,7 +9801,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>103</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>103</v>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>467</v>
+        <v>440</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>103</v>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="12" t="s">
-        <v>468</v>
+        <v>441</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>103</v>
@@ -9883,7 +9883,7 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>103</v>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>103</v>
@@ -9927,7 +9927,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>103</v>
@@ -9946,7 +9946,7 @@
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>103</v>
@@ -9969,7 +9969,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>103</v>
@@ -9992,7 +9992,7 @@
         <v>4</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>497</v>
+        <v>470</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>103</v>
@@ -10011,7 +10011,7 @@
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>103</v>
@@ -10030,7 +10030,7 @@
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>504</v>
+        <v>477</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>103</v>
@@ -10049,7 +10049,7 @@
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>505</v>
+        <v>478</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>103</v>
@@ -10068,7 +10068,7 @@
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>103</v>
@@ -10089,7 +10089,7 @@
         <v>8</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>103</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>103</v>
@@ -10129,7 +10129,7 @@
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>510</v>
+        <v>483</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>103</v>
@@ -10152,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>511</v>
+        <v>484</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>103</v>
@@ -10171,7 +10171,7 @@
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>103</v>
@@ -10190,7 +10190,7 @@
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>103</v>
@@ -10213,7 +10213,7 @@
         <v>15</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>103</v>
@@ -11225,13 +11225,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>301</v>
+        <v>582</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>168</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>15</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>308</v>
+        <v>583</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>167</v>
@@ -11267,7 +11267,7 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>167</v>
@@ -11290,7 +11290,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>167</v>
@@ -11313,7 +11313,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>340</v>
+        <v>584</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>167</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>347</v>
+        <v>585</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>167</v>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>348</v>
+        <v>586</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>167</v>
@@ -11378,7 +11378,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>167</v>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>167</v>
@@ -11422,7 +11422,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>386</v>
+        <v>359</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>167</v>
@@ -11441,7 +11441,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>401</v>
+        <v>374</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>167</v>
@@ -11460,7 +11460,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>409</v>
+        <v>382</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>167</v>
@@ -11483,7 +11483,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>167</v>
@@ -11506,7 +11506,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>167</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>415</v>
+        <v>388</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>167</v>
@@ -11546,7 +11546,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="16" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>167</v>
@@ -11569,7 +11569,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>420</v>
+        <v>393</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>167</v>
@@ -11588,7 +11588,7 @@
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>425</v>
+        <v>398</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>167</v>
@@ -11607,7 +11607,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>167</v>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>167</v>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>167</v>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>167</v>
@@ -11689,7 +11689,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>167</v>
@@ -11712,7 +11712,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>167</v>
@@ -11735,7 +11735,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>167</v>
@@ -11754,7 +11754,7 @@
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>462</v>
+        <v>435</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>167</v>
@@ -11777,7 +11777,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>470</v>
+        <v>443</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>167</v>
@@ -11800,7 +11800,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>471</v>
+        <v>444</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>167</v>
@@ -11823,7 +11823,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>167</v>
@@ -11846,7 +11846,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>167</v>
@@ -11869,7 +11869,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>167</v>
@@ -11892,7 +11892,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>167</v>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>167</v>
@@ -11932,7 +11932,7 @@
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>502</v>
+        <v>475</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>167</v>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>167</v>
@@ -11972,7 +11972,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>167</v>
@@ -11995,7 +11995,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>515</v>
+        <v>488</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>167</v>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>167</v>
@@ -12035,7 +12035,7 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="12" t="s">
-        <v>533</v>
+        <v>587</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>167</v>
@@ -12054,7 +12054,7 @@
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="12" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>167</v>
@@ -12073,7 +12073,7 @@
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="12" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>167</v>
@@ -12081,7 +12081,7 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>15</v>
@@ -12100,7 +12100,7 @@
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>18</v>
@@ -12111,7 +12111,7 @@
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>167</v>
@@ -12119,7 +12119,7 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>591</v>
+        <v>551</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>18</v>
@@ -12130,7 +12130,7 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="12" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>167</v>
@@ -12138,7 +12138,7 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>593</v>
+        <v>552</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>8</v>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="12" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G46" s="8" t="s">
         <v>167</v>
@@ -12159,7 +12159,7 @@
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>595</v>
+        <v>553</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>18</v>
@@ -12170,7 +12170,7 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="12" t="s">
-        <v>596</v>
+        <v>554</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>167</v>
@@ -12178,18 +12178,18 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>597</v>
+        <v>555</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="12" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>167</v>
@@ -12197,18 +12197,18 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>599</v>
+        <v>556</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="12" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>167</v>
@@ -12216,7 +12216,7 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>601</v>
+        <v>557</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>13</v>
@@ -12231,7 +12231,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>167</v>
@@ -12239,18 +12239,18 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>602</v>
+        <v>558</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>167</v>
@@ -12258,18 +12258,18 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>604</v>
+        <v>559</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="12" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>167</v>
@@ -12277,18 +12277,18 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>606</v>
+        <v>560</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>167</v>
@@ -12296,18 +12296,18 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>607</v>
+        <v>561</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>167</v>
@@ -12315,18 +12315,18 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>609</v>
+        <v>562</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>167</v>
@@ -12334,18 +12334,18 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>610</v>
+        <v>563</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>167</v>
@@ -12353,18 +12353,18 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>612</v>
+        <v>564</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>167</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="58" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>13</v>
@@ -12387,7 +12387,7 @@
         <v>10</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>618</v>
+        <v>567</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>167</v>
@@ -12458,7 +12458,7 @@
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>309</v>
+        <v>592</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>209</v>
@@ -12494,7 +12494,7 @@
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>209</v>
@@ -12530,7 +12530,7 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>209</v>
@@ -12566,7 +12566,7 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>209</v>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>355</v>
+        <v>593</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>209</v>
@@ -12644,7 +12644,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>209</v>
@@ -12680,7 +12680,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>209</v>
@@ -12716,7 +12716,7 @@
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>209</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>365</v>
+        <v>594</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>209</v>
@@ -12794,7 +12794,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>209</v>
@@ -12834,7 +12834,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>209</v>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>209</v>
@@ -12912,7 +12912,7 @@
         <v>7</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>209</v>
@@ -12948,7 +12948,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>209</v>
@@ -12988,7 +12988,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>209</v>
@@ -13024,7 +13024,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>209</v>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>428</v>
+        <v>401</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>209</v>
@@ -13098,7 +13098,7 @@
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>429</v>
+        <v>402</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>209</v>
@@ -13138,7 +13138,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>209</v>
@@ -13174,7 +13174,7 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>442</v>
+        <v>415</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>209</v>
@@ -13210,7 +13210,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>209</v>
@@ -13246,7 +13246,7 @@
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>461</v>
+        <v>434</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>209</v>
@@ -13282,7 +13282,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>209</v>
@@ -13322,7 +13322,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>469</v>
+        <v>442</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>209</v>
@@ -13358,7 +13358,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>209</v>
@@ -13396,7 +13396,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>209</v>
@@ -13430,7 +13430,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>525</v>
+        <v>596</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>209</v>
@@ -13470,7 +13470,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>209</v>
@@ -13510,7 +13510,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>209</v>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>209</v>
@@ -13584,7 +13584,7 @@
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="13" t="s">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>209</v>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="13" t="s">
-        <v>538</v>
+        <v>598</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>209</v>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="13" t="s">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>209</v>
@@ -13700,7 +13700,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>209</v>
@@ -13740,7 +13740,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>209</v>
@@ -13776,7 +13776,7 @@
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="13" t="s">
-        <v>542</v>
+        <v>508</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>209</v>
@@ -19403,7 +19403,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>292</v>
+        <v>602</v>
       </c>
       <c r="G2" s="11" t="s">
         <v>246</v>
@@ -19426,7 +19426,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>246</v>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>246</v>
@@ -19470,7 +19470,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>246</v>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>324</v>
+        <v>603</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>246</v>
@@ -19512,7 +19512,7 @@
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>345</v>
+        <v>604</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>246</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>353</v>
+        <v>605</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>246</v>
@@ -19552,7 +19552,7 @@
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>246</v>
@@ -19575,7 +19575,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>380</v>
+        <v>606</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>246</v>
@@ -19598,7 +19598,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>246</v>
@@ -19617,7 +19617,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="G12" s="11" t="s">
         <v>246</v>
@@ -19634,7 +19634,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>246</v>
@@ -19653,7 +19653,7 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>246</v>
@@ -19672,7 +19672,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>246</v>
@@ -19691,7 +19691,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>246</v>
@@ -19710,7 +19710,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>246</v>
@@ -19729,7 +19729,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>246</v>
@@ -19752,7 +19752,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>492</v>
+        <v>465</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>246</v>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>246</v>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>246</v>
@@ -19813,7 +19813,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="G22" s="11" t="s">
         <v>246</v>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>509</v>
+        <v>482</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>246</v>
@@ -19857,7 +19857,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>246</v>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>246</v>
@@ -22475,7 +22475,7 @@
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>271</v>
@@ -22494,7 +22494,7 @@
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>271</v>
@@ -22513,7 +22513,7 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>271</v>
@@ -22532,7 +22532,7 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>271</v>
@@ -22551,7 +22551,7 @@
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>271</v>
@@ -22570,7 +22570,7 @@
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>271</v>
@@ -22589,7 +22589,7 @@
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>544</v>
+        <v>607</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>271</v>
@@ -22608,7 +22608,7 @@
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>545</v>
+        <v>608</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>271</v>
@@ -22627,7 +22627,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>271</v>
@@ -22646,7 +22646,7 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>543</v>
+        <v>509</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>271</v>
@@ -22665,7 +22665,7 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>271</v>
@@ -22684,7 +22684,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>271</v>
@@ -22703,7 +22703,7 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>271</v>
@@ -22722,7 +22722,7 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>458</v>
+        <v>431</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>271</v>
@@ -22741,7 +22741,7 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>271</v>
@@ -22760,7 +22760,7 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>463</v>
+        <v>436</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>271</v>
@@ -22779,7 +22779,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>271</v>
@@ -22802,7 +22802,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>271</v>
@@ -22821,7 +22821,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>547</v>
+        <v>609</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>271</v>
@@ -22840,7 +22840,7 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>271</v>
@@ -22848,7 +22848,7 @@
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>548</v>
+        <v>511</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>15</v>
@@ -22859,7 +22859,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>549</v>
+        <v>512</v>
       </c>
       <c r="G22" s="8"/>
     </row>

--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A5464C-CE41-4223-B4F5-E83F3AAD71ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA50BF36-E102-4B2C-8FD3-AA144E0147A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="8" r:id="rId1"/>
@@ -4280,7 +4280,7 @@
         <v>25</v>
       </c>
       <c r="E17" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>325</v>

--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3361EE-C754-49AD-A0CC-AEE068D72E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB46915-2CCB-4D1F-A70A-E79A7FD8E40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="Cristianesimo" sheetId="2" r:id="rId2"/>
-    <sheet name="Mitologia Norrena" sheetId="3" r:id="rId3"/>
-    <sheet name="Animismo" sheetId="4" r:id="rId4"/>
-    <sheet name="Egiziane" sheetId="5" r:id="rId5"/>
-    <sheet name="Ph-DakGaph" sheetId="6" r:id="rId6"/>
-    <sheet name="Ombre Maya" sheetId="7" r:id="rId7"/>
-    <sheet name="Neutre" sheetId="8" r:id="rId8"/>
+    <sheet name="Taoismo" sheetId="9" r:id="rId3"/>
+    <sheet name="Mitologia Norrena" sheetId="3" r:id="rId4"/>
+    <sheet name="Animismo" sheetId="4" r:id="rId5"/>
+    <sheet name="Egiziane" sheetId="5" r:id="rId6"/>
+    <sheet name="Ph-DakGaph" sheetId="6" r:id="rId7"/>
+    <sheet name="Ombre Maya" sheetId="7" r:id="rId8"/>
+    <sheet name="Neutre" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="638">
   <si>
     <t>Nome Carta</t>
   </si>
@@ -122,9 +123,6 @@
     <t>Biblioteca Apostolica</t>
   </si>
   <si>
-    <t>Ogni volta che giochi una Benedizione o una Maledizione, aggiungi 1 Segnalino su questa carta. Puoi rimuovere 3 Segnalini da questa carta: cerca nel tuo reliquiario una Benedizione o Maledizione, rivelala e aggiungila alla tua mano. Poi mischia il reliquiario.</t>
-  </si>
-  <si>
     <t>Biblioteca d'Oro</t>
   </si>
   <si>
@@ -179,9 +177,6 @@
     <t>Custode della Creazione</t>
   </si>
   <si>
-    <t>Per giocare questa carta, devi scomunicare dal tuo cimitero una copia di "Giorno 1", "Giorno 2", "Giorno 3", "Giorno 4", "Giorno 5", "Giorno 6" e "Giorno 7". Questa carta non può essere bersagliata da effetti.</t>
-  </si>
-  <si>
     <t>Dio, il Creatore</t>
   </si>
   <si>
@@ -221,15 +216,9 @@
     <t>Giorno 1: Cieli e Terra</t>
   </si>
   <si>
-    <t>Puoi giocare una carta Artefatto dalla tua mano pagando metà del suo costo di Ispirazione (arrotondato per eccesso).</t>
-  </si>
-  <si>
     <t>Giorno 2: Cielo Terrestre</t>
   </si>
   <si>
-    <t>Nessun Santo può attaccare in questo turno.</t>
-  </si>
-  <si>
     <t>Giorno 3: Terre e Mari</t>
   </si>
   <si>
@@ -239,33 +228,18 @@
     <t>Giorno 4: Stelle</t>
   </si>
   <si>
-    <t>Guarda le prime 3 carte del tuo reliquiario e rimettile in cima nello stesso ordine. Poi puoi mischiare il reliquiario.</t>
-  </si>
-  <si>
     <t>Giorno 5: Creature del Mare</t>
   </si>
   <si>
-    <t>Questo Santo può attaccare solo se la tua Ispirazione rimanente è superiore a 2.</t>
-  </si>
-  <si>
     <t>Giorno 6: Creature di Terra</t>
   </si>
   <si>
-    <t>Questo Santo può attaccare solo se la tua Ispirazione rimanente è inferiore a 5.</t>
-  </si>
-  <si>
     <t>Giorno 7: Riposo</t>
   </si>
   <si>
-    <t>Scegli un Santo avversario. Quel Santo non può attaccare durante il prossimo turno dell'avversario.</t>
-  </si>
-  <si>
     <t>Giorno Festivo</t>
   </si>
   <si>
-    <t>Puoi avere massimo 3 copie di "Giorno Festivo" nel tuo reliquiario. Fino a quando questa carta è sul campo, nessun giocatore può effettuare attacchi. Questo effetto termina quando un giocatore pesca una carta.</t>
-  </si>
-  <si>
     <t>Giudizio Universale</t>
   </si>
   <si>
@@ -1932,13 +1906,49 @@
   </si>
   <si>
     <t>Aggiungi alla tua mano un santo dal tuo cimitero. Se controlli Altare dei Sette Sigilli con almeno 6 Segnalini Sigillo, puoi scegliere qualsiasi tipo di carta, escluso Sesto Sigillo.</t>
+  </si>
+  <si>
+    <t>Scegli una carta artefatto nel tuo reliquiario e posizionala in campo pagando metà della sua ispirazione.</t>
+  </si>
+  <si>
+    <t>Finche questa carta è presente sul terreno, dimezza il peccato che ricevi per attacchi diretti o per morte di santi.</t>
+  </si>
+  <si>
+    <t>Guarda le prime 3 carte del tuo reliquiario. Pesca ogni carta con "Giorno" nel suo nome.</t>
+  </si>
+  <si>
+    <t>Quando questo santo attacca, dopo il calcolo dei danni, aumenta la sua fede di +2 e la sua forza di +3</t>
+  </si>
+  <si>
+    <t>Quando questo santo attacca, dopo il calcolo dei danni, aumenta la sua fede di +3 e la sua forza di +2</t>
+  </si>
+  <si>
+    <t>Finche questa carta è sul terreno, per ogni carta "Giorno" giocata, rimuovi 1 peccato da te stesso e infliggi 2 peccato al tuo avversario.</t>
+  </si>
+  <si>
+    <t>Scegli un santo avversario. Rimuovi peccato pari alla sua forza.</t>
+  </si>
+  <si>
+    <t>TAO-1</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finche questa carta è sul terreno, ogni volta che infliggi peccato al giocatore avversario, rimuovilo da te stesso. </t>
+  </si>
+  <si>
+    <t>Ogni volta che viene giocata una Benedizione o una Maledizione, aggiungi 1 Segnalino su questa carta. Puoi rimuovere 3 Segnalini da questa carta: cerca nel tuo reliquiario una Benedizione o Maledizione, rivelala e aggiungila alla tua mano. Poi mischia il reliquiario.</t>
+  </si>
+  <si>
+    <t>Per giocare questa carta, devi scomunicare dal terreno o cimitero una copia di "Giorno 1", "Giorno 2", "Giorno 3", "Giorno 4", "Giorno 5", "Giorno 6" e "Giorno 7". Finche questa carta è sul terreno non può essere bersagliata da effetti di carte del tuo avversario.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1999,16 +2009,29 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2016,11 +2039,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2085,6 +2139,31 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -3461,28 +3540,28 @@
         <v>6</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3490,202 +3569,202 @@
         <v>11</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C3" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="F3" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>178</v>
-      </c>
       <c r="G3" s="20" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="G4" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="20" t="s">
         <v>170</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C5" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>168</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="E6" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>177</v>
-      </c>
       <c r="G6" s="20" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B8" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>181</v>
-      </c>
       <c r="I8" s="20" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3873,7 +3952,7 @@
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>31</v>
+        <v>636</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>11</v>
@@ -3881,20 +3960,20 @@
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="14">
         <v>5</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>11</v>
@@ -3902,7 +3981,7 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>17</v>
@@ -3917,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>11</v>
@@ -3925,20 +4004,20 @@
     </row>
     <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="14">
         <v>10</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>11</v>
@@ -3946,7 +4025,7 @@
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>8</v>
@@ -3959,7 +4038,7 @@
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>11</v>
@@ -3967,20 +4046,20 @@
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="14">
         <v>8</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>11</v>
@@ -3988,7 +4067,7 @@
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>27</v>
@@ -3999,7 +4078,7 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>11</v>
@@ -4007,7 +4086,7 @@
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>17</v>
@@ -4022,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>11</v>
@@ -4030,13 +4109,13 @@
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="14">
         <v>30</v>
@@ -4044,8 +4123,8 @@
       <c r="E16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>50</v>
+      <c r="F16" s="30" t="s">
+        <v>637</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>11</v>
@@ -4053,13 +4132,13 @@
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="14">
         <v>25</v>
@@ -4068,7 +4147,7 @@
         <v>20</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>11</v>
@@ -4076,7 +4155,7 @@
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>21</v>
@@ -4087,7 +4166,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>11</v>
@@ -4095,13 +4174,13 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" s="14">
         <v>3</v>
@@ -4110,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>11</v>
@@ -4118,7 +4197,7 @@
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
@@ -4131,7 +4210,7 @@
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>11</v>
@@ -4139,18 +4218,18 @@
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>11</v>
@@ -4158,7 +4237,7 @@
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>27</v>
@@ -4169,7 +4248,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>64</v>
+        <v>626</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>11</v>
@@ -4177,18 +4256,20 @@
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="14"/>
+      <c r="D23" s="14">
+        <v>5</v>
+      </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>66</v>
+        <v>627</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>11</v>
@@ -4196,18 +4277,18 @@
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>11</v>
@@ -4215,18 +4296,18 @@
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>70</v>
+        <v>628</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>11</v>
@@ -4234,22 +4315,22 @@
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>72</v>
+        <v>629</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>11</v>
@@ -4257,22 +4338,22 @@
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
       </c>
       <c r="E27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>74</v>
+        <v>630</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>11</v>
@@ -4280,18 +4361,20 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="14"/>
+        <v>8</v>
+      </c>
+      <c r="C28" s="14">
+        <v>7</v>
+      </c>
+      <c r="D28" s="14">
+        <v>7</v>
+      </c>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>76</v>
+        <v>631</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>11</v>
@@ -4299,7 +4382,7 @@
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>27</v>
@@ -4310,7 +4393,7 @@
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="12" t="s">
-        <v>78</v>
+        <v>632</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>11</v>
@@ -4318,18 +4401,18 @@
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>11</v>
@@ -4337,13 +4420,13 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D31" s="14">
         <v>5</v>
@@ -4352,7 +4435,7 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>11</v>
@@ -4360,7 +4443,7 @@
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>17</v>
@@ -4375,7 +4458,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>11</v>
@@ -4383,7 +4466,7 @@
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>17</v>
@@ -4398,7 +4481,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>11</v>
@@ -4406,7 +4489,7 @@
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>27</v>
@@ -4417,7 +4500,7 @@
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>11</v>
@@ -4425,7 +4508,7 @@
     </row>
     <row r="35" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>17</v>
@@ -4440,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>11</v>
@@ -4448,7 +4531,7 @@
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>17</v>
@@ -4463,7 +4546,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>11</v>
@@ -4471,18 +4554,18 @@
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>11</v>
@@ -4490,7 +4573,7 @@
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>17</v>
@@ -4505,7 +4588,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>11</v>
@@ -4513,13 +4596,13 @@
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D39" s="14">
         <v>4</v>
@@ -4528,7 +4611,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>11</v>
@@ -4536,7 +4619,7 @@
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>17</v>
@@ -4551,7 +4634,7 @@
         <v>6</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>11</v>
@@ -4559,7 +4642,7 @@
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>21</v>
@@ -4570,7 +4653,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>11</v>
@@ -4578,18 +4661,18 @@
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>11</v>
@@ -4597,18 +4680,18 @@
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>11</v>
@@ -4616,13 +4699,13 @@
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D44" s="14">
         <v>1</v>
@@ -4631,7 +4714,7 @@
         <v>3</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>11</v>
@@ -4639,18 +4722,18 @@
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>11</v>
@@ -4658,7 +4741,7 @@
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>27</v>
@@ -4669,7 +4752,7 @@
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>11</v>
@@ -4677,7 +4760,7 @@
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>17</v>
@@ -4692,7 +4775,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>11</v>
@@ -4700,18 +4783,18 @@
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>11</v>
@@ -4719,7 +4802,7 @@
     </row>
     <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>21</v>
@@ -4730,7 +4813,7 @@
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="12" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>11</v>
@@ -4738,7 +4821,7 @@
     </row>
     <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>21</v>
@@ -4749,7 +4832,7 @@
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="12" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>11</v>
@@ -4757,7 +4840,7 @@
     </row>
     <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
@@ -4768,7 +4851,7 @@
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>11</v>
@@ -4776,20 +4859,20 @@
     </row>
     <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D52" s="14">
         <v>3</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>11</v>
@@ -4797,7 +4880,7 @@
     </row>
     <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
@@ -4808,7 +4891,7 @@
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>11</v>
@@ -4816,18 +4899,18 @@
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>11</v>
@@ -4835,7 +4918,7 @@
     </row>
     <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>21</v>
@@ -4846,7 +4929,7 @@
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="12" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>11</v>
@@ -4854,7 +4937,7 @@
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>27</v>
@@ -4865,7 +4948,7 @@
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="12" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>11</v>
@@ -4873,18 +4956,18 @@
     </row>
     <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>11</v>
@@ -4892,7 +4975,7 @@
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>8</v>
@@ -4905,7 +4988,7 @@
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>11</v>
@@ -4913,7 +4996,7 @@
     </row>
     <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>21</v>
@@ -4924,7 +5007,7 @@
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>11</v>
@@ -4932,7 +5015,7 @@
     </row>
     <row r="60" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>8</v>
@@ -4945,7 +5028,7 @@
       </c>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>11</v>
@@ -4953,7 +5036,7 @@
     </row>
     <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>8</v>
@@ -4966,7 +5049,7 @@
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="12" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>11</v>
@@ -4974,7 +5057,7 @@
     </row>
     <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>17</v>
@@ -4989,7 +5072,7 @@
         <v>3</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>11</v>
@@ -4997,18 +5080,18 @@
     </row>
     <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="12" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>11</v>
@@ -5016,7 +5099,7 @@
     </row>
     <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>17</v>
@@ -5031,7 +5114,7 @@
         <v>5</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>11</v>
@@ -5039,7 +5122,7 @@
     </row>
     <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>17</v>
@@ -5054,7 +5137,7 @@
         <v>4</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>11</v>
@@ -5062,18 +5145,18 @@
     </row>
     <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="12" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>11</v>
@@ -5081,7 +5164,7 @@
     </row>
     <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>27</v>
@@ -5092,7 +5175,7 @@
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="12" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>11</v>
@@ -5100,18 +5183,18 @@
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68" s="12" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>11</v>
@@ -5119,7 +5202,7 @@
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>27</v>
@@ -5130,7 +5213,7 @@
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="12" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>11</v>
@@ -7140,6 +7223,65 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE01ED5-E7BA-454F-8C68-AAA74B6A13BE}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="166" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>634</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="27">
+        <v>8</v>
+      </c>
+      <c r="D2" s="27">
+        <v>5</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>633</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7179,7 +7321,7 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>27</v>
@@ -7190,15 +7332,15 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="16" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>21</v>
@@ -7209,15 +7351,15 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>17</v>
@@ -7232,34 +7374,34 @@
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>8</v>
@@ -7272,21 +7414,21 @@
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="15">
         <v>3</v>
@@ -7295,15 +7437,15 @@
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>8</v>
@@ -7316,21 +7458,21 @@
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" s="15">
         <v>8</v>
@@ -7339,15 +7481,15 @@
         <v>2</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>17</v>
@@ -7362,15 +7504,15 @@
         <v>6</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>17</v>
@@ -7385,15 +7527,15 @@
         <v>2</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
@@ -7406,42 +7548,42 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="16" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="15">
         <v>8</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" s="15">
         <v>3</v>
@@ -7450,15 +7592,15 @@
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>17</v>
@@ -7473,61 +7615,61 @@
         <v>8</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
@@ -7536,15 +7678,15 @@
         <v>2</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>17</v>
@@ -7559,15 +7701,15 @@
         <v>4</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>17</v>
@@ -7582,15 +7724,15 @@
         <v>3</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>17</v>
@@ -7605,15 +7747,15 @@
         <v>3</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>21</v>
@@ -7624,21 +7766,21 @@
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D23" s="15">
         <v>10</v>
@@ -7647,15 +7789,15 @@
         <v>8</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>13</v>
@@ -7668,31 +7810,31 @@
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="16" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="15">
         <v>10</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8742,7 +8884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8785,7 +8927,7 @@
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>17</v>
@@ -8800,18 +8942,18 @@
         <v>3</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>17</v>
@@ -8826,24 +8968,24 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D4" s="14">
         <v>10</v>
@@ -8852,24 +8994,24 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -8878,18 +9020,18 @@
         <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>17</v>
@@ -8904,24 +9046,24 @@
         <v>3</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="14">
         <v>2</v>
@@ -8930,15 +9072,15 @@
         <v>2</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>17</v>
@@ -8953,36 +9095,36 @@
         <v>8</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="14">
         <v>6</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
@@ -8995,32 +9137,32 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>21</v>
@@ -9031,15 +9173,15 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>8</v>
@@ -9052,21 +9194,21 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="14">
         <v>6</v>
@@ -9075,15 +9217,15 @@
         <v>4</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>8</v>
@@ -9096,15 +9238,15 @@
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>21</v>
@@ -9115,36 +9257,36 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>27</v>
@@ -9155,42 +9297,42 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -9199,45 +9341,45 @@
         <v>4</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H20" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D21" s="14">
         <v>2</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
@@ -9246,21 +9388,21 @@
         <v>2</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -9269,15 +9411,15 @@
         <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>21</v>
@@ -9288,21 +9430,21 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -9311,15 +9453,15 @@
         <v>1</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>27</v>
@@ -9330,56 +9472,56 @@
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
@@ -9394,15 +9536,15 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>17</v>
@@ -9417,15 +9559,15 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -9440,46 +9582,46 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H31" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="12" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H32" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -9488,18 +9630,18 @@
         <v>4</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H33" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>17</v>
@@ -9514,40 +9656,40 @@
         <v>6</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H34" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H35" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
@@ -9560,18 +9702,18 @@
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H36" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>21</v>
@@ -9582,18 +9724,18 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H37" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>27</v>
@@ -9604,15 +9746,15 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="12" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>21</v>
@@ -9623,53 +9765,53 @@
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="12" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
@@ -9682,36 +9824,36 @@
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D43" s="14">
         <v>8</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
@@ -9724,15 +9866,15 @@
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="12" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>27</v>
@@ -9743,15 +9885,15 @@
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -9764,15 +9906,15 @@
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>17</v>
@@ -9787,18 +9929,18 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>27</v>
@@ -9809,15 +9951,15 @@
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>17</v>
@@ -9832,24 +9974,24 @@
         <v>2</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D50" s="14">
         <v>4</v>
@@ -9858,18 +10000,18 @@
         <v>4</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H50" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>21</v>
@@ -9880,34 +10022,34 @@
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>21</v>
@@ -9918,37 +10060,37 @@
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="14">
@@ -9958,21 +10100,21 @@
         <v>8</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H55" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="14">
@@ -9982,15 +10124,15 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>21</v>
@@ -10001,15 +10143,15 @@
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>17</v>
@@ -10022,18 +10164,18 @@
         <v>0</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="H58" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>21</v>
@@ -10044,40 +10186,40 @@
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D61" s="14">
         <v>25</v>
@@ -10086,10 +10228,10 @@
         <v>15</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11040,7 +11182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11083,13 +11225,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -11098,21 +11240,21 @@
         <v>1</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" s="14">
         <v>25</v>
@@ -11121,15 +11263,15 @@
         <v>15</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>27</v>
@@ -11140,21 +11282,21 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="14">
         <v>5</v>
@@ -11163,21 +11305,21 @@
         <v>5</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
@@ -11186,15 +11328,15 @@
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>8</v>
@@ -11207,36 +11349,36 @@
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>17</v>
@@ -11251,15 +11393,15 @@
         <v>4</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
@@ -11272,15 +11414,15 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>17</v>
@@ -11295,15 +11437,15 @@
         <v>5</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>27</v>
@@ -11314,40 +11456,40 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
@@ -11356,21 +11498,21 @@
         <v>3</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
@@ -11379,15 +11521,15 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
@@ -11400,40 +11542,40 @@
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="16" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18" s="14">
         <v>25</v>
@@ -11442,15 +11584,15 @@
         <v>10</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>27</v>
@@ -11461,15 +11603,15 @@
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>21</v>
@@ -11480,15 +11622,15 @@
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
@@ -11501,15 +11643,15 @@
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
@@ -11522,15 +11664,15 @@
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
@@ -11543,40 +11685,40 @@
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -11585,15 +11727,15 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>17</v>
@@ -11608,34 +11750,34 @@
         <v>20</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>17</v>
@@ -11650,15 +11792,15 @@
         <v>1</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
@@ -11673,21 +11815,21 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D30" s="14">
         <v>8</v>
@@ -11696,21 +11838,21 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D31" s="14">
         <v>2</v>
@@ -11719,21 +11861,21 @@
         <v>2</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D32" s="14">
         <v>2</v>
@@ -11742,15 +11884,15 @@
         <v>2</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>17</v>
@@ -11765,36 +11907,36 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="14">
         <v>10</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>21</v>
@@ -11805,18 +11947,18 @@
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14">
@@ -11826,34 +11968,34 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>17</v>
@@ -11868,15 +12010,15 @@
         <v>2</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
@@ -11889,15 +12031,15 @@
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>21</v>
@@ -11908,91 +12050,91 @@
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="12" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="12" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="12" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="12" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="12" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>27</v>
@@ -12003,15 +12145,15 @@
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="12" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>8</v>
@@ -12024,15 +12166,15 @@
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="12" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>27</v>
@@ -12043,15 +12185,15 @@
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="12" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>21</v>
@@ -12062,15 +12204,15 @@
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="12" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>21</v>
@@ -12081,15 +12223,15 @@
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="12" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>17</v>
@@ -12104,15 +12246,15 @@
         <v>6</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>21</v>
@@ -12123,15 +12265,15 @@
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>21</v>
@@ -12142,15 +12284,15 @@
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="12" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>21</v>
@@ -12161,15 +12303,15 @@
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>21</v>
@@ -12180,15 +12322,15 @@
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>21</v>
@@ -12199,15 +12341,15 @@
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>21</v>
@@ -12218,15 +12360,15 @@
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>21</v>
@@ -12237,21 +12379,21 @@
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D58" s="8">
         <v>25</v>
@@ -12260,10 +12402,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -12275,7 +12417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -12318,7 +12460,7 @@
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>13</v>
@@ -12331,10 +12473,10 @@
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -12356,21 +12498,21 @@
     </row>
     <row r="3" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -12392,7 +12534,7 @@
     </row>
     <row r="4" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>27</v>
@@ -12403,10 +12545,10 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -12428,7 +12570,7 @@
     </row>
     <row r="5" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>27</v>
@@ -12439,10 +12581,10 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -12464,23 +12606,23 @@
     </row>
     <row r="6" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -12502,13 +12644,13 @@
     </row>
     <row r="7" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D7" s="14">
         <v>1</v>
@@ -12517,10 +12659,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -12542,7 +12684,7 @@
     </row>
     <row r="8" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>27</v>
@@ -12553,10 +12695,10 @@
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -12578,7 +12720,7 @@
     </row>
     <row r="9" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>21</v>
@@ -12589,10 +12731,10 @@
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -12614,7 +12756,7 @@
     </row>
     <row r="10" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
@@ -12627,10 +12769,10 @@
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -12652,7 +12794,7 @@
     </row>
     <row r="11" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>17</v>
@@ -12667,10 +12809,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -12692,7 +12834,7 @@
     </row>
     <row r="12" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>17</v>
@@ -12707,10 +12849,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -12732,7 +12874,7 @@
     </row>
     <row r="13" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
@@ -12745,10 +12887,10 @@
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -12770,7 +12912,7 @@
     </row>
     <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>17</v>
@@ -12785,10 +12927,10 @@
         <v>7</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -12810,21 +12952,21 @@
     </row>
     <row r="15" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -12846,13 +12988,13 @@
     </row>
     <row r="16" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="14">
         <v>35</v>
@@ -12861,10 +13003,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -12886,7 +13028,7 @@
     </row>
     <row r="17" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>21</v>
@@ -12897,10 +13039,10 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -12922,23 +13064,23 @@
     </row>
     <row r="18" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" s="14">
         <v>10</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -12960,21 +13102,21 @@
     </row>
     <row r="19" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -12996,13 +13138,13 @@
     </row>
     <row r="20" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -13011,10 +13153,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -13036,21 +13178,21 @@
     </row>
     <row r="21" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -13072,21 +13214,21 @@
     </row>
     <row r="22" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -13108,21 +13250,21 @@
     </row>
     <row r="23" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -13144,7 +13286,7 @@
     </row>
     <row r="24" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>27</v>
@@ -13155,10 +13297,10 @@
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -13180,13 +13322,13 @@
     </row>
     <row r="25" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
@@ -13195,10 +13337,10 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -13220,21 +13362,21 @@
     </row>
     <row r="26" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -13256,10 +13398,10 @@
     </row>
     <row r="27" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14">
@@ -13269,10 +13411,10 @@
         <v>1</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -13294,19 +13436,19 @@
     </row>
     <row r="28" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -13328,7 +13470,7 @@
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>17</v>
@@ -13343,10 +13485,10 @@
         <v>4</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -13368,13 +13510,13 @@
     </row>
     <row r="30" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" s="14">
         <v>30</v>
@@ -13383,10 +13525,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -13408,7 +13550,7 @@
     </row>
     <row r="31" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>8</v>
@@ -13421,10 +13563,10 @@
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -13446,21 +13588,21 @@
     </row>
     <row r="32" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="13" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -13482,7 +13624,7 @@
     </row>
     <row r="33" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>8</v>
@@ -13495,10 +13637,10 @@
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="13" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -13520,7 +13662,7 @@
     </row>
     <row r="34" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>8</v>
@@ -13533,10 +13675,10 @@
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="13" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -13558,13 +13700,13 @@
     </row>
     <row r="35" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35" s="8">
         <v>3</v>
@@ -13573,10 +13715,10 @@
         <v>6</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -13598,13 +13740,13 @@
     </row>
     <row r="36" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" s="8">
         <v>7</v>
@@ -13613,10 +13755,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -13638,21 +13780,21 @@
     </row>
     <row r="37" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="13" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -19219,7 +19361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -19261,13 +19403,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" s="14">
         <v>7</v>
@@ -19276,21 +19418,21 @@
         <v>7</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="14">
         <v>3</v>
@@ -19299,15 +19441,15 @@
         <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
@@ -19320,21 +19462,21 @@
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="14">
         <v>8</v>
@@ -19343,36 +19485,36 @@
         <v>6</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="14">
         <v>5</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>8</v>
@@ -19385,55 +19527,55 @@
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="14">
         <v>8</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>17</v>
@@ -19448,15 +19590,15 @@
         <v>6</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>17</v>
@@ -19471,15 +19613,15 @@
         <v>4</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>21</v>
@@ -19490,32 +19632,32 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>27</v>
@@ -19526,15 +19668,15 @@
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>27</v>
@@ -19545,15 +19687,15 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>27</v>
@@ -19564,53 +19706,53 @@
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>17</v>
@@ -19625,15 +19767,15 @@
         <v>6</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>8</v>
@@ -19646,18 +19788,18 @@
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>28</v>
@@ -19667,34 +19809,34 @@
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>13</v>
@@ -19707,15 +19849,15 @@
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>17</v>
@@ -19730,31 +19872,31 @@
         <v>5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22293,7 +22435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -22336,45 +22478,45 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>21</v>
@@ -22385,110 +22527,110 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>27</v>
@@ -22499,15 +22641,15 @@
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>27</v>
@@ -22518,15 +22660,15 @@
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>21</v>
@@ -22537,15 +22679,15 @@
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>27</v>
@@ -22556,34 +22698,34 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>27</v>
@@ -22594,34 +22736,34 @@
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>27</v>
@@ -22632,15 +22774,15 @@
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>21</v>
@@ -22651,21 +22793,21 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
         <v>5</v>
@@ -22674,34 +22816,34 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>27</v>
@@ -22712,29 +22854,29 @@
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BA60CF-1477-4256-A64A-9A60CFF55796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A2797-43CB-472A-A0D3-83E183A2DA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,9 +273,6 @@
     <t>Li Tieguai</t>
   </si>
   <si>
-    <t>Quando un tuo Ba Xian viene distrutto, puoi invece ridurre la Forza di questa carta di 1 e annullare quella distruzione. Se la Forza di questa carta e 0, distruggila.</t>
-  </si>
-  <si>
     <t>Han Xiangzi</t>
   </si>
   <si>
@@ -2275,6 +2272,9 @@
   </si>
   <si>
     <t>Alias</t>
+  </si>
+  <si>
+    <t>Quando un tuo Ba Xian viene distrutto, puoi invece ridurre la Forza di questa carta di 2 e annullare quella distruzione. Se la Forza di questa carta e 0, distruggila.</t>
   </si>
 </sst>
 </file>
@@ -2385,7 +2385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2475,39 +2475,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="85">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3510,6 +3482,31 @@
         <name val="Arial"/>
         <family val="2"/>
       </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
       <alignment horizontal="center" vertical="center"/>
       <border>
         <left/>
@@ -3783,16 +3780,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabella1" displayName="Tabella1" ref="A1:G69" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabella1" displayName="Tabella1" ref="A1:G69" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68">
   <autoFilter ref="A1:G69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nome Carta" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Croci" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Fede" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Forza" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Effetto" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Espansione" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nome Carta" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tipo" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Croci" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Fede" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Forza" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Effetto" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Espansione" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3809,103 +3806,103 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Forza" dataDxfId="73"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Effetto" dataDxfId="72"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Espansione" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{0869AEA3-AC6D-4925-83EF-573F42CE0402}" name="Alias" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{0869AEA3-AC6D-4925-83EF-573F42CE0402}" name="Alias" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabella2" displayName="Tabella2" ref="A1:G25" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabella2" displayName="Tabella2" ref="A1:G25" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58">
   <autoFilter ref="A1:G25" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Nome Carta" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Tipo" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Croci" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Fede" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Forza" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Effetto" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Espansione" dataDxfId="51"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Nome Carta" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Tipo" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Croci" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Fede" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Forza" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Effetto" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Espansione" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabella3" displayName="Tabella3" ref="A1:G61" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabella3" displayName="Tabella3" ref="A1:G61" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48">
   <autoFilter ref="A1:G61" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Nome Carta" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Tipo" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Croci" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Fede" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Forza" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Effetto" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Espansione" dataDxfId="41"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Nome Carta" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Tipo" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Croci" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Fede" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Forza" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Effetto" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Espansione" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella4" displayName="Tabella4" ref="A1:G58" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabella4" displayName="Tabella4" ref="A1:G58" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38">
   <autoFilter ref="A1:G58" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Nome Carta" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Tipo" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Croci" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Fede" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Forza" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Effetto" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Espansione" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Nome Carta" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Tipo" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Croci" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Fede" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Forza" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Effetto" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Espansione" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabella5" displayName="Tabella5" ref="A1:G37" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabella5" displayName="Tabella5" ref="A1:G37" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28">
   <autoFilter ref="A1:G37" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Nome Carta" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Tipo" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Croci" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Fede" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Forza" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Effetto" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Espansione" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Nome Carta" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Tipo" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Croci" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Fede" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Forza" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Effetto" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Espansione" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabella6" displayName="Tabella6" ref="A1:G25" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabella6" displayName="Tabella6" ref="A1:G25" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18">
   <autoFilter ref="A1:G25" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Nome Carta" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Tipo" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Croci" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Fede" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Forza" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Effetto" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Espansione" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Nome Carta" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Tipo" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Croci" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Fede" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Forza" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Effetto" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Espansione" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabella7" displayName="Tabella7" ref="A1:G22" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabella7" displayName="Tabella7" ref="A1:G22" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8">
   <autoFilter ref="A1:G22" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Nome Carta" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Tipo" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Croci" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Fede" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Forza" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Effetto" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Espansione" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Nome Carta" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Tipo" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Croci" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Fede" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Forza" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Effetto" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Espansione" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4121,231 +4118,231 @@
         <v>6</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>118</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="C2" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="D2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>127</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="F3" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="G3" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>136</v>
-      </c>
       <c r="E4" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="E5" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="F5" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="G5" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="H5" s="20" t="s">
-        <v>142</v>
-      </c>
       <c r="I5" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>144</v>
-      </c>
       <c r="E6" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="E7" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>147</v>
-      </c>
       <c r="G7" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4396,55 +4393,55 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D2" s="14">
         <v>3</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D3" s="14">
         <v>9</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D4" s="14">
         <v>5</v>
@@ -4453,122 +4450,122 @@
         <v>4</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D8" s="14">
         <v>8</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D9" s="14">
         <v>5</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D10" s="14">
         <v>0</v>
@@ -4577,103 +4574,103 @@
         <v>3</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D11" s="14">
         <v>10</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="14">
         <v>6</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D13" s="14">
         <v>8</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="14">
         <v>6</v>
@@ -4682,21 +4679,21 @@
         <v>2</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16" s="14">
         <v>30</v>
@@ -4705,21 +4702,21 @@
         <v>0</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" s="14">
         <v>25</v>
@@ -4728,40 +4725,40 @@
         <v>20</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D19" s="14">
         <v>3</v>
@@ -4770,139 +4767,139 @@
         <v>3</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
@@ -4911,21 +4908,21 @@
         <v>9</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -4934,15 +4931,15 @@
         <v>6</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
@@ -4955,59 +4952,59 @@
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D31" s="14">
         <v>5</v>
@@ -5016,21 +5013,21 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" s="14">
         <v>2</v>
@@ -5039,21 +5036,21 @@
         <v>4</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D33" s="14">
         <v>5</v>
@@ -5062,40 +5059,40 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D35" s="14">
         <v>6</v>
@@ -5104,21 +5101,21 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D36" s="14">
         <v>1</v>
@@ -5127,40 +5124,40 @@
         <v>2</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="14">
         <v>6</v>
@@ -5169,21 +5166,21 @@
         <v>3</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D39" s="14">
         <v>4</v>
@@ -5192,21 +5189,21 @@
         <v>3</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D40" s="14">
         <v>10</v>
@@ -5215,78 +5212,78 @@
         <v>6</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D44" s="14">
         <v>1</v>
@@ -5295,59 +5292,59 @@
         <v>3</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D47" s="14">
         <v>4</v>
@@ -5356,295 +5353,295 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D52" s="14">
         <v>3</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D58" s="14">
         <v>3</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D60" s="14">
         <v>6</v>
       </c>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D61" s="14">
         <v>2</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D62" s="14">
         <v>8</v>
@@ -5653,40 +5650,40 @@
         <v>3</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D64" s="14">
         <v>5</v>
@@ -5695,21 +5692,21 @@
         <v>5</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D65" s="14">
         <v>7</v>
@@ -5718,86 +5715,86 @@
         <v>4</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7838,7 +7835,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -7861,7 +7858,7 @@
       <c r="G2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="31"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -7881,7 +7878,7 @@
       <c r="G3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="31"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
@@ -7901,7 +7898,7 @@
       <c r="G4" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="31"/>
+      <c r="H4" s="29"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
@@ -7921,7 +7918,7 @@
       <c r="G5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="31"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -7941,7 +7938,7 @@
       <c r="G6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="31"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
@@ -7961,7 +7958,7 @@
       <c r="G7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="31"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
@@ -7981,7 +7978,7 @@
       <c r="G8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="31"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
@@ -8001,7 +7998,7 @@
       <c r="G9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="31"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -8021,7 +8018,7 @@
       <c r="G10" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="31"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -8041,7 +8038,7 @@
       <c r="G11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="31"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
@@ -8061,7 +8058,7 @@
       <c r="G12" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="31"/>
+      <c r="H12" s="29"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
@@ -8081,7 +8078,7 @@
       <c r="G13" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="31"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
@@ -8101,7 +8098,7 @@
       <c r="G14" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="31"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
@@ -8121,7 +8118,7 @@
       <c r="G15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="31"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
@@ -8141,7 +8138,7 @@
       <c r="G16" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="31"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
@@ -8161,7 +8158,7 @@
       <c r="G17" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="31"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
@@ -8183,7 +8180,7 @@
       <c r="G18" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="31"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
@@ -8205,7 +8202,7 @@
       <c r="G19" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="31"/>
+      <c r="H19" s="29"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
@@ -8227,7 +8224,7 @@
       <c r="G20" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="31"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
@@ -8249,7 +8246,7 @@
       <c r="G21" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="31"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
@@ -8271,7 +8268,7 @@
       <c r="G22" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="31"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
@@ -8293,7 +8290,7 @@
       <c r="G23" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="31"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
@@ -8315,7 +8312,7 @@
       <c r="G24" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="31"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
@@ -8339,7 +8336,7 @@
       <c r="G25" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="31"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
@@ -8363,7 +8360,7 @@
       <c r="G26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="31"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
@@ -8387,7 +8384,7 @@
       <c r="G27" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="31"/>
+      <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
@@ -8411,7 +8408,7 @@
       <c r="G28" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="31"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
@@ -8435,7 +8432,7 @@
       <c r="G29" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="31"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
@@ -8459,7 +8456,7 @@
       <c r="G30" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="31"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
@@ -8483,7 +8480,7 @@
       <c r="G31" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="31"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
@@ -8507,7 +8504,7 @@
       <c r="G32" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="31"/>
+      <c r="H32" s="29"/>
     </row>
     <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
@@ -8531,7 +8528,7 @@
       <c r="G33" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="29" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8557,7 +8554,7 @@
       <c r="G34" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="29" t="s">
         <v>77</v>
       </c>
     </row>
@@ -8578,18 +8575,18 @@
         <v>8</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>81</v>
+        <v>748</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>59</v>
@@ -8604,18 +8601,18 @@
         <v>5</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>59</v>
@@ -8630,18 +8627,18 @@
         <v>4</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>59</v>
@@ -8656,24 +8653,24 @@
         <v>6</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="29">
         <v>10</v>
@@ -8682,18 +8679,18 @@
         <v>15</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>59</v>
@@ -8708,18 +8705,18 @@
         <v>10</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="29" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>12</v>
@@ -8730,16 +8727,16 @@
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H41" s="31"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B42" s="22" t="s">
         <v>12</v>
@@ -8750,16 +8747,16 @@
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="F42" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="31"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="22" t="s">
         <v>12</v>
@@ -8770,16 +8767,16 @@
       <c r="D43" s="23"/>
       <c r="E43" s="23"/>
       <c r="F43" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="31"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B44" s="22" t="s">
         <v>12</v>
@@ -8790,16 +8787,16 @@
       <c r="D44" s="23"/>
       <c r="E44" s="23"/>
       <c r="F44" s="24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="31"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="22" t="s">
         <v>12</v>
@@ -8810,16 +8807,16 @@
       <c r="D45" s="23"/>
       <c r="E45" s="23"/>
       <c r="F45" s="24" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="31"/>
+      <c r="H45" s="29"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B46" s="22" t="s">
         <v>12</v>
@@ -8830,16 +8827,16 @@
       <c r="D46" s="23"/>
       <c r="E46" s="23"/>
       <c r="F46" s="24" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="31"/>
+      <c r="H46" s="29"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B47" s="22" t="s">
         <v>31</v>
@@ -8850,16 +8847,16 @@
       <c r="D47" s="23"/>
       <c r="E47" s="23"/>
       <c r="F47" s="24" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="31"/>
+      <c r="H47" s="29"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B48" s="22" t="s">
         <v>31</v>
@@ -8870,16 +8867,16 @@
       <c r="D48" s="23"/>
       <c r="E48" s="23"/>
       <c r="F48" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="31"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>31</v>
@@ -8890,16 +8887,16 @@
       <c r="D49" s="23"/>
       <c r="E49" s="23"/>
       <c r="F49" s="24" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H49" s="31"/>
+      <c r="H49" s="29"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" s="22" t="s">
         <v>31</v>
@@ -8910,16 +8907,16 @@
       <c r="D50" s="23"/>
       <c r="E50" s="23"/>
       <c r="F50" s="24" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H50" s="31"/>
+      <c r="H50" s="29"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B51" s="22" t="s">
         <v>8</v>
@@ -8932,16 +8929,16 @@
       </c>
       <c r="E51" s="23"/>
       <c r="F51" s="24" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="31"/>
+      <c r="H51" s="29"/>
     </row>
     <row r="52" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B52" s="22" t="s">
         <v>8</v>
@@ -8954,16 +8951,16 @@
       </c>
       <c r="E52" s="23"/>
       <c r="F52" s="24" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="31"/>
+      <c r="H52" s="29"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B53" s="22" t="s">
         <v>8</v>
@@ -8976,16 +8973,16 @@
       </c>
       <c r="E53" s="23"/>
       <c r="F53" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H53" s="31"/>
+      <c r="H53" s="29"/>
     </row>
     <row r="54" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B54" s="22" t="s">
         <v>54</v>
@@ -8998,16 +8995,16 @@
       </c>
       <c r="E54" s="23"/>
       <c r="F54" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H54" s="31"/>
+      <c r="H54" s="29"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>54</v>
@@ -9020,16 +9017,16 @@
       </c>
       <c r="E55" s="23"/>
       <c r="F55" s="24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H55" s="31"/>
+      <c r="H55" s="29"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B56" s="22" t="s">
         <v>54</v>
@@ -9042,12 +9039,12 @@
       </c>
       <c r="E56" s="23"/>
       <c r="F56" s="24" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H56" s="31"/>
+      <c r="H56" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9097,51 +9094,51 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4" s="15">
         <v>15</v>
@@ -9150,61 +9147,61 @@
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D6" s="15">
         <v>4</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7" s="15">
         <v>3</v>
@@ -9213,42 +9210,42 @@
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="15">
         <v>4</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="15">
         <v>8</v>
@@ -9257,21 +9254,21 @@
         <v>2</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="15">
         <v>25</v>
@@ -9280,21 +9277,21 @@
         <v>6</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D11" s="15">
         <v>6</v>
@@ -9303,63 +9300,63 @@
         <v>2</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="15">
         <v>4</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D13" s="15">
         <v>8</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D14" s="15">
         <v>3</v>
@@ -9368,21 +9365,21 @@
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D15" s="15">
         <v>5</v>
@@ -9391,61 +9388,61 @@
         <v>8</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
@@ -9454,21 +9451,21 @@
         <v>2</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
@@ -9477,21 +9474,21 @@
         <v>4</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
@@ -9500,21 +9497,21 @@
         <v>3</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="15">
         <v>2</v>
@@ -9523,40 +9520,40 @@
         <v>3</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D23" s="15">
         <v>10</v>
@@ -9565,52 +9562,52 @@
         <v>8</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D24" s="15">
         <v>8</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D25" s="15">
         <v>10</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10703,13 +10700,13 @@
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" s="14">
         <v>8</v>
@@ -10718,24 +10715,24 @@
         <v>3</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H2" t="s">
         <v>344</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="14">
         <v>2</v>
@@ -10744,24 +10741,24 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" t="s">
         <v>347</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="H3" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" s="14">
         <v>10</v>
@@ -10770,24 +10767,24 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -10796,24 +10793,24 @@
         <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D6" s="14">
         <v>7</v>
@@ -10822,24 +10819,24 @@
         <v>3</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D7" s="14">
         <v>2</v>
@@ -10848,21 +10845,21 @@
         <v>2</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D8" s="14">
         <v>2</v>
@@ -10871,120 +10868,120 @@
         <v>8</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="14">
         <v>6</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="14">
         <v>2</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>363</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>364</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" s="14">
         <v>5</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D14" s="14">
         <v>6</v>
@@ -10993,122 +10990,122 @@
         <v>4</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="14">
         <v>5</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -11117,45 +11114,45 @@
         <v>4</v>
       </c>
       <c r="F20" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" t="s">
         <v>383</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D21" s="14">
         <v>2</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
@@ -11164,21 +11161,21 @@
         <v>2</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -11187,40 +11184,40 @@
         <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -11229,81 +11226,81 @@
         <v>1</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
@@ -11312,21 +11309,21 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D30" s="14">
         <v>2</v>
@@ -11335,21 +11332,21 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" s="14">
         <v>3</v>
@@ -11358,46 +11355,46 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H31" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H32" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -11406,24 +11403,24 @@
         <v>4</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H33" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D34" s="14">
         <v>6</v>
@@ -11432,271 +11429,271 @@
         <v>6</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H34" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D36" s="14">
         <v>4</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D42" s="14">
         <v>6</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D43" s="14">
         <v>8</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D44" s="14">
         <v>5</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D46" s="14">
         <v>8</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D47" s="14">
         <v>8</v>
@@ -11705,43 +11702,43 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H47" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D49" s="14">
         <v>5</v>
@@ -11750,24 +11747,24 @@
         <v>2</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H49" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D50" s="14">
         <v>4</v>
@@ -11776,97 +11773,97 @@
         <v>4</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H50" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>453</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="14">
@@ -11876,21 +11873,21 @@
         <v>8</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H55" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="14">
@@ -11900,102 +11897,102 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D58" s="14"/>
       <c r="E58" s="14">
         <v>0</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H58" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D61" s="14">
         <v>25</v>
@@ -12004,10 +12001,10 @@
         <v>15</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13001,13 +12998,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -13016,21 +13013,21 @@
         <v>1</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D3" s="14">
         <v>25</v>
@@ -13039,40 +13036,40 @@
         <v>15</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D5" s="14">
         <v>5</v>
@@ -13081,21 +13078,21 @@
         <v>5</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
@@ -13104,63 +13101,63 @@
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D7" s="14">
         <v>6</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="14">
         <v>4</v>
@@ -13169,42 +13166,42 @@
         <v>4</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="14">
         <v>5</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D11" s="14">
         <v>9</v>
@@ -13213,59 +13210,59 @@
         <v>5</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
@@ -13274,21 +13271,21 @@
         <v>3</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
@@ -13297,61 +13294,61 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D16" s="14">
         <v>8</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D18" s="14">
         <v>25</v>
@@ -13360,141 +13357,141 @@
         <v>10</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21" s="14">
         <v>8</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -13503,21 +13500,21 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D26" s="14">
         <v>20</v>
@@ -13526,40 +13523,40 @@
         <v>20</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
@@ -13568,21 +13565,21 @@
         <v>1</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" s="14">
         <v>4</v>
@@ -13591,21 +13588,21 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D30" s="14">
         <v>8</v>
@@ -13614,21 +13611,21 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D31" s="14">
         <v>2</v>
@@ -13637,21 +13634,21 @@
         <v>2</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D32" s="14">
         <v>2</v>
@@ -13660,21 +13657,21 @@
         <v>2</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D33" s="14">
         <v>6</v>
@@ -13683,58 +13680,58 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D34" s="14">
         <v>10</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14">
@@ -13744,40 +13741,40 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="14">
         <v>3</v>
@@ -13786,234 +13783,234 @@
         <v>2</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D39" s="14">
         <v>6</v>
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="12" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="12" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="12" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="12" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D46" s="8">
         <v>6</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="12" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="12" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" s="8">
         <v>6</v>
@@ -14022,154 +14019,154 @@
         <v>6</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="12" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D58" s="8">
         <v>25</v>
@@ -14178,10 +14175,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -14236,23 +14233,23 @@
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D2" s="14">
         <v>4</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -14274,21 +14271,21 @@
     </row>
     <row r="3" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -14310,21 +14307,21 @@
     </row>
     <row r="4" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -14346,21 +14343,21 @@
     </row>
     <row r="5" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -14382,23 +14379,23 @@
     </row>
     <row r="6" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -14420,13 +14417,13 @@
     </row>
     <row r="7" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D7" s="14">
         <v>1</v>
@@ -14435,10 +14432,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -14460,21 +14457,21 @@
     </row>
     <row r="8" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -14496,21 +14493,21 @@
     </row>
     <row r="9" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -14532,23 +14529,23 @@
     </row>
     <row r="10" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" s="14">
         <v>6</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -14570,13 +14567,13 @@
     </row>
     <row r="11" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" s="14">
         <v>6</v>
@@ -14585,10 +14582,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -14610,13 +14607,13 @@
     </row>
     <row r="12" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D12" s="14">
         <v>2</v>
@@ -14625,10 +14622,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -14650,23 +14647,23 @@
     </row>
     <row r="13" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="14">
         <v>7</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -14688,13 +14685,13 @@
     </row>
     <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D14" s="14">
         <v>5</v>
@@ -14703,10 +14700,10 @@
         <v>7</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -14728,21 +14725,21 @@
     </row>
     <row r="15" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -14764,13 +14761,13 @@
     </row>
     <row r="16" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D16" s="14">
         <v>35</v>
@@ -14779,10 +14776,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -14804,21 +14801,21 @@
     </row>
     <row r="17" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -14840,23 +14837,23 @@
     </row>
     <row r="18" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" s="14">
         <v>10</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -14878,21 +14875,21 @@
     </row>
     <row r="19" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -14914,13 +14911,13 @@
     </row>
     <row r="20" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -14929,10 +14926,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -14954,21 +14951,21 @@
     </row>
     <row r="21" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -14990,21 +14987,21 @@
     </row>
     <row r="22" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -15026,21 +15023,21 @@
     </row>
     <row r="23" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -15062,21 +15059,21 @@
     </row>
     <row r="24" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -15098,13 +15095,13 @@
     </row>
     <row r="25" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
@@ -15113,10 +15110,10 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -15138,21 +15135,21 @@
     </row>
     <row r="26" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -15174,10 +15171,10 @@
     </row>
     <row r="27" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14">
@@ -15187,10 +15184,10 @@
         <v>1</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -15212,19 +15209,19 @@
     </row>
     <row r="28" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -15246,13 +15243,13 @@
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D29" s="14">
         <v>4</v>
@@ -15261,10 +15258,10 @@
         <v>4</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -15286,13 +15283,13 @@
     </row>
     <row r="30" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D30" s="14">
         <v>30</v>
@@ -15301,10 +15298,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -15326,23 +15323,23 @@
     </row>
     <row r="31" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D31" s="8">
         <v>5</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -15364,21 +15361,21 @@
     </row>
     <row r="32" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="13" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -15400,23 +15397,23 @@
     </row>
     <row r="33" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D33" s="8">
         <v>8</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="13" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -15438,23 +15435,23 @@
     </row>
     <row r="34" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D34" s="8">
         <v>6</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="13" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -15476,13 +15473,13 @@
     </row>
     <row r="35" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D35" s="8">
         <v>3</v>
@@ -15491,10 +15488,10 @@
         <v>6</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -15516,13 +15513,13 @@
     </row>
     <row r="36" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D36" s="8">
         <v>7</v>
@@ -15531,10 +15528,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -15556,21 +15553,21 @@
     </row>
     <row r="37" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -21179,13 +21176,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D2" s="14">
         <v>7</v>
@@ -21194,21 +21191,21 @@
         <v>7</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" s="14">
         <v>3</v>
@@ -21217,42 +21214,42 @@
         <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D4" s="14">
         <v>5</v>
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" s="14">
         <v>8</v>
@@ -21261,103 +21258,103 @@
         <v>6</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D6" s="14">
         <v>5</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="14">
         <v>10</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D8" s="14">
         <v>8</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D10" s="14">
         <v>6</v>
@@ -21366,21 +21363,21 @@
         <v>6</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D11" s="14">
         <v>4</v>
@@ -21389,152 +21386,152 @@
         <v>4</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D19" s="14">
         <v>1</v>
@@ -21543,103 +21540,103 @@
         <v>6</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D20" s="14">
         <v>10</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D21" s="14">
         <v>1</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" s="14">
         <v>5</v>
@@ -21648,31 +21645,31 @@
         <v>5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24254,336 +24251,336 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D19" s="14">
         <v>5</v>
@@ -24592,67 +24589,67 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Holy War.xlsx
+++ b/Holy War.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\Holy-War-Python-Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2A2797-43CB-472A-A0D3-83E183A2DA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE26190D-A4A0-4628-A4A3-CD03F60687DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="2565" windowWidth="21600" windowHeight="10140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -228,9 +228,6 @@
     <t>Guardiano dello Yin</t>
   </si>
   <si>
-    <t>Ogni volta che il tuo avversario ottiene Ispirazione, rimuovi 1 Peccato da te stesso.</t>
-  </si>
-  <si>
     <t>Guardiana dello Yang</t>
   </si>
   <si>
@@ -321,9 +318,6 @@
     <t>Eco dei Nomi Immortali</t>
   </si>
   <si>
-    <t>Rivela la tua mano. Per ogni Ba Xian rivelato, pesca 1 carta fino a un massimo di 3. Poi rimetti nel reliquiario 1 carta dalla tua mano.</t>
-  </si>
-  <si>
     <t>Ponte tra Cielo e Polvere</t>
   </si>
   <si>
@@ -2262,9 +2256,6 @@
     <t>Per ogni Ba Xian diverso sul terreno, i tuoi santi ricevono 2 danni in meno dagli attacchi avversari</t>
   </si>
   <si>
-    <t>Ogni volta che un Ba Xian entra in campo (dalla mano, reliquiario o cimitero), aggiungi 1 Segnalino Armonia su questa carta. Puoi rimuovere 3 Segnalini Armonia: pesca 1 carta o aggiungi alla mano un Ba Xian dal tuo cimitero.</t>
-  </si>
-  <si>
     <t>Finche questa carta è sul terreno, ogni volta che peschi una carta, i tuoi Ba Xian ottengono +1 Fede e +1 Forza.</t>
   </si>
   <si>
@@ -2275,6 +2266,15 @@
   </si>
   <si>
     <t>Quando un tuo Ba Xian viene distrutto, puoi invece ridurre la Forza di questa carta di 2 e annullare quella distruzione. Se la Forza di questa carta e 0, distruggila.</t>
+  </si>
+  <si>
+    <t>Ogni volta che il tuo avversario pesca una carta, rimuovi 1 peccato da te stesso.</t>
+  </si>
+  <si>
+    <t>Puoi giocare questa carta solo se hai un Ba Xian sul terreno, gioca questa carta per evocare un Ba Xian con nome diverso dalla tua mano al terreno.</t>
+  </si>
+  <si>
+    <t>Finche questa carta + sul terreno, ogni tuo santo ottiene +3 forza per ogni Ba Xian presente sul tuo terreno e +3 fede per ogni Ba Xian nel tuo cimitero.</t>
   </si>
 </sst>
 </file>
@@ -2385,7 +2385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2467,13 +2467,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3798,6 +3804,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabella8" displayName="Tabella8" ref="A1:H56" totalsRowShown="0" headerRowDxfId="80" dataDxfId="79" tableBorderDxfId="78">
   <autoFilter ref="A1:H56" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H56">
+    <sortCondition ref="A1:A56"/>
+  </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Nome Carta" dataDxfId="77"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Tipo" dataDxfId="76"/>
@@ -4118,231 +4127,231 @@
         <v>6</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>116</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="D2" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="E2" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="G2" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>125</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="F3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="G3" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="I3" s="20" t="s">
         <v>130</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="E4" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="I4" s="20" t="s">
         <v>130</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="F5" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="G5" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="H5" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>141</v>
-      </c>
       <c r="I5" s="20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C6" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" s="20" t="s">
         <v>121</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>146</v>
-      </c>
       <c r="G7" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F8" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="I8" s="20" t="s">
         <v>130</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="20" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4393,55 +4402,55 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D2" s="14">
         <v>3</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D3" s="14">
         <v>9</v>
       </c>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D4" s="14">
         <v>5</v>
@@ -4450,122 +4459,122 @@
         <v>4</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D8" s="14">
         <v>8</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D9" s="14">
         <v>5</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D10" s="14">
         <v>0</v>
@@ -4574,103 +4583,103 @@
         <v>3</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D11" s="14">
         <v>10</v>
       </c>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="14">
         <v>6</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D13" s="14">
         <v>8</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D15" s="14">
         <v>6</v>
@@ -4679,21 +4688,21 @@
         <v>2</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D16" s="14">
         <v>30</v>
@@ -4702,21 +4711,21 @@
         <v>0</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D17" s="14">
         <v>25</v>
@@ -4725,40 +4734,40 @@
         <v>20</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D19" s="14">
         <v>3</v>
@@ -4767,139 +4776,139 @@
         <v>3</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
@@ -4908,21 +4917,21 @@
         <v>9</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
@@ -4931,15 +4940,15 @@
         <v>6</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>8</v>
@@ -4952,59 +4961,59 @@
       </c>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D31" s="14">
         <v>5</v>
@@ -5013,21 +5022,21 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D32" s="14">
         <v>2</v>
@@ -5036,21 +5045,21 @@
         <v>4</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D33" s="14">
         <v>5</v>
@@ -5059,40 +5068,40 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D35" s="14">
         <v>6</v>
@@ -5101,21 +5110,21 @@
         <v>0</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D36" s="14">
         <v>1</v>
@@ -5124,40 +5133,40 @@
         <v>2</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D38" s="14">
         <v>6</v>
@@ -5166,21 +5175,21 @@
         <v>3</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D39" s="14">
         <v>4</v>
@@ -5189,21 +5198,21 @@
         <v>3</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D40" s="14">
         <v>10</v>
@@ -5212,78 +5221,78 @@
         <v>6</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D44" s="14">
         <v>1</v>
@@ -5292,59 +5301,59 @@
         <v>3</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D47" s="14">
         <v>4</v>
@@ -5353,295 +5362,295 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D50" s="14"/>
       <c r="E50" s="14"/>
       <c r="F50" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D52" s="14">
         <v>3</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D55" s="14"/>
       <c r="E55" s="14"/>
       <c r="F55" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D56" s="14"/>
       <c r="E56" s="14"/>
       <c r="F56" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D58" s="14">
         <v>3</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D60" s="14">
         <v>6</v>
       </c>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D61" s="14">
         <v>2</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D62" s="14">
         <v>8</v>
@@ -5650,40 +5659,40 @@
         <v>3</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D63" s="14"/>
       <c r="E63" s="14"/>
       <c r="F63" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D64" s="14">
         <v>5</v>
@@ -5692,21 +5701,21 @@
         <v>5</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D65" s="14">
         <v>7</v>
@@ -5715,86 +5724,86 @@
         <v>4</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
       <c r="F66" s="12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
       <c r="F67" s="12" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
       <c r="F68" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7835,230 +7844,246 @@
         <v>6</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>7</v>
+        <v>107</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C2" s="23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2" s="23"/>
       <c r="F2" s="24" t="s">
-        <v>9</v>
+        <v>742</v>
       </c>
       <c r="G2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="29"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="23">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
       <c r="F3" s="24" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="29"/>
+      <c r="H3" s="28"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="23"/>
       <c r="F4" s="24" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="29"/>
+      <c r="H4" s="28"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" s="23">
-        <v>4</v>
-      </c>
-      <c r="D5" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="D5" s="23">
+        <v>5</v>
+      </c>
       <c r="E5" s="23"/>
       <c r="F5" s="24" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="28"/>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" s="23">
-        <v>3</v>
-      </c>
-      <c r="D6" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="23">
+        <v>4</v>
+      </c>
       <c r="E6" s="23"/>
       <c r="F6" s="24" t="s">
-        <v>19</v>
+        <v>740</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="29"/>
+      <c r="H6" s="28"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="23">
-        <v>5</v>
-      </c>
-      <c r="D7" s="23"/>
+        <v>7</v>
+      </c>
+      <c r="D7" s="23">
+        <v>7</v>
+      </c>
       <c r="E7" s="23"/>
       <c r="F7" s="24" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="29"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H7" s="28"/>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="22" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="23">
-        <v>4</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+        <v>59</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="23">
+        <v>10</v>
+      </c>
+      <c r="E8" s="23">
+        <v>15</v>
+      </c>
       <c r="F8" s="24" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="29"/>
+      <c r="H8" s="28" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
       <c r="F9" s="24" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="29"/>
+      <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C10" s="23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="29"/>
+      <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="23"/>
       <c r="F11" s="24" t="s">
-        <v>29</v>
+        <v>732</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="29"/>
+      <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C12" s="23">
+        <v>7</v>
+      </c>
+      <c r="D12" s="23">
         <v>4</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
+      <c r="E12" s="23">
+        <v>5</v>
+      </c>
       <c r="F12" s="24" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="29"/>
+      <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
@@ -8078,269 +8103,293 @@
       <c r="G13" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="29"/>
+      <c r="H13" s="28"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C14" s="23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="23"/>
       <c r="F14" s="24" t="s">
-        <v>36</v>
+        <v>747</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="28"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C15" s="23">
-        <v>5</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+        <v>2</v>
+      </c>
+      <c r="D15" s="23">
+        <v>2</v>
+      </c>
+      <c r="E15" s="23">
+        <v>1</v>
+      </c>
       <c r="F15" s="24" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="29"/>
+      <c r="H15" s="28"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="24" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="29"/>
+      <c r="H16" s="28"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C17" s="23">
-        <v>3</v>
-      </c>
-      <c r="D17" s="23"/>
+        <v>7</v>
+      </c>
+      <c r="D17" s="23">
+        <v>7</v>
+      </c>
       <c r="E17" s="23"/>
       <c r="F17" s="24" t="s">
-        <v>42</v>
+        <v>743</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="29"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="28"/>
+    </row>
+    <row r="18" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C18" s="23">
-        <v>6</v>
-      </c>
-      <c r="D18" s="23">
-        <v>5</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D18" s="23"/>
       <c r="E18" s="23"/>
       <c r="F18" s="24" t="s">
-        <v>44</v>
+        <v>737</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="29"/>
+      <c r="H18" s="28"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C19" s="23">
         <v>4</v>
       </c>
       <c r="D19" s="23">
+        <v>2</v>
+      </c>
+      <c r="E19" s="23">
         <v>4</v>
       </c>
-      <c r="E19" s="23"/>
       <c r="F19" s="24" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="29"/>
+      <c r="H19" s="28"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C20" s="23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="23">
-        <v>6</v>
-      </c>
-      <c r="E20" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="E20" s="23">
+        <v>2</v>
+      </c>
       <c r="F20" s="24" t="s">
-        <v>48</v>
+        <v>746</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="29"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C21" s="23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D21" s="23">
         <v>7</v>
       </c>
-      <c r="E21" s="23"/>
+      <c r="E21" s="23">
+        <v>5</v>
+      </c>
       <c r="F21" s="24" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="29"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H21" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="C22" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D22" s="23">
-        <v>3</v>
-      </c>
-      <c r="E22" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="E22" s="23">
+        <v>5</v>
+      </c>
       <c r="F22" s="24" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="29"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H22" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C23" s="23">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23" s="23">
         <v>8</v>
       </c>
-      <c r="E23" s="23"/>
+      <c r="E23" s="23">
+        <v>4</v>
+      </c>
       <c r="F23" s="24" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="29"/>
+      <c r="H23" s="28" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C24" s="23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="23">
-        <v>7</v>
-      </c>
-      <c r="E24" s="23"/>
+        <v>5</v>
+      </c>
+      <c r="E24" s="23">
+        <v>4</v>
+      </c>
       <c r="F24" s="24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="29"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H24" s="28"/>
+    </row>
+    <row r="25" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="23">
         <v>5</v>
       </c>
       <c r="E25" s="23">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>60</v>
+        <v>745</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="29"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H25" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>59</v>
@@ -8352,15 +8401,17 @@
         <v>4</v>
       </c>
       <c r="E26" s="23">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="29"/>
+      <c r="H26" s="28" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
@@ -8384,382 +8435,322 @@
       <c r="G27" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="29"/>
+      <c r="H27" s="28"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C28" s="23">
-        <v>4</v>
-      </c>
-      <c r="D28" s="23">
-        <v>4</v>
-      </c>
-      <c r="E28" s="23">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
       <c r="F28" s="24" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="G28" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="29"/>
+      <c r="H28" s="28"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="23">
+        <v>3</v>
+      </c>
+      <c r="E29" s="23">
         <v>2</v>
       </c>
-      <c r="E29" s="23">
-        <v>4</v>
-      </c>
       <c r="F29" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="29"/>
+      <c r="H29" s="28"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C30" s="23">
-        <v>3</v>
-      </c>
-      <c r="D30" s="23">
-        <v>3</v>
-      </c>
-      <c r="E30" s="23">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
       <c r="F30" s="24" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="29"/>
+      <c r="H30" s="28"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C31" s="23">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D31" s="23">
-        <v>2</v>
-      </c>
-      <c r="E31" s="23">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E31" s="23"/>
       <c r="F31" s="24" t="s">
-        <v>72</v>
+        <v>748</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="29"/>
+      <c r="H31" s="28"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C32" s="23">
+        <v>6</v>
+      </c>
+      <c r="D32" s="23">
         <v>7</v>
       </c>
-      <c r="D32" s="23">
-        <v>4</v>
-      </c>
-      <c r="E32" s="23">
-        <v>5</v>
-      </c>
+      <c r="E32" s="23"/>
       <c r="F32" s="24" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="29"/>
-    </row>
-    <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H32" s="28"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C33" s="23">
-        <v>6</v>
-      </c>
-      <c r="D33" s="23">
-        <v>4</v>
-      </c>
-      <c r="E33" s="23">
-        <v>7</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
       <c r="F33" s="24" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="29">
+      <c r="H33" s="28"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="30">
+        <v>4</v>
+      </c>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="31" t="s">
+        <v>735</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="28"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="30">
+        <v>4</v>
+      </c>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="31" t="s">
+        <v>733</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="28"/>
+    </row>
+    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="30">
         <v>5</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="28"/>
+    </row>
+    <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="30">
+        <v>3</v>
+      </c>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="31" t="s">
+        <v>734</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="28"/>
+    </row>
+    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="30">
+        <v>2</v>
+      </c>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="28"/>
+    </row>
+    <row r="39" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="30">
+        <v>3</v>
+      </c>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="31" t="s">
+        <v>738</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="28"/>
+    </row>
+    <row r="40" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="30">
         <v>4</v>
       </c>
-      <c r="E34" s="29">
-        <v>5</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34" s="7" t="s">
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H34" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="29">
-        <v>5</v>
-      </c>
-      <c r="D35" s="29">
-        <v>5</v>
-      </c>
-      <c r="E35" s="29">
-        <v>8</v>
-      </c>
-      <c r="F35" s="30" t="s">
-        <v>748</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="29">
-        <v>4</v>
-      </c>
-      <c r="D36" s="29">
-        <v>7</v>
-      </c>
-      <c r="E36" s="29">
-        <v>5</v>
-      </c>
-      <c r="F36" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="29">
-        <v>4</v>
-      </c>
-      <c r="D37" s="29">
-        <v>8</v>
-      </c>
-      <c r="E37" s="29">
-        <v>4</v>
-      </c>
-      <c r="F37" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="29">
-        <v>6</v>
-      </c>
-      <c r="D38" s="29">
-        <v>4</v>
-      </c>
-      <c r="E38" s="29">
-        <v>6</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H38" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="29">
-        <v>10</v>
-      </c>
-      <c r="E39" s="29">
-        <v>15</v>
-      </c>
-      <c r="F39" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" s="29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="29">
-        <v>10</v>
-      </c>
-      <c r="D40" s="29">
-        <v>6</v>
-      </c>
-      <c r="E40" s="29">
-        <v>10</v>
-      </c>
-      <c r="F40" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H40" s="29" t="s">
-        <v>77</v>
-      </c>
+      <c r="H40" s="28"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="B41" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="24" t="s">
-        <v>734</v>
+        <v>29</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H41" s="29"/>
+      <c r="H41" s="28"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="B42" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="F42" s="24" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="29"/>
+      <c r="H42" s="28"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C43" s="23">
         <v>4</v>
@@ -8767,284 +8758,302 @@
       <c r="D43" s="23"/>
       <c r="E43" s="23"/>
       <c r="F43" s="24" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="29"/>
+      <c r="H43" s="28"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C44" s="23">
+        <v>8</v>
+      </c>
+      <c r="D44" s="23">
         <v>5</v>
       </c>
-      <c r="D44" s="23"/>
       <c r="E44" s="23"/>
       <c r="F44" s="24" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="29"/>
+      <c r="H44" s="28"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C45" s="23">
-        <v>3</v>
-      </c>
-      <c r="D45" s="23"/>
+        <v>9</v>
+      </c>
+      <c r="D45" s="23">
+        <v>6</v>
+      </c>
       <c r="E45" s="23"/>
       <c r="F45" s="24" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="29"/>
+      <c r="H45" s="28"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C46" s="23">
-        <v>4</v>
-      </c>
-      <c r="D46" s="23"/>
+        <v>3</v>
+      </c>
+      <c r="D46" s="23">
+        <v>3</v>
+      </c>
       <c r="E46" s="23"/>
       <c r="F46" s="24" t="s">
-        <v>737</v>
+        <v>52</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="29"/>
+      <c r="H46" s="28"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C47" s="23">
-        <v>4</v>
-      </c>
-      <c r="D47" s="23"/>
+        <v>5</v>
+      </c>
+      <c r="D47" s="23">
+        <v>6</v>
+      </c>
       <c r="E47" s="23"/>
       <c r="F47" s="24" t="s">
-        <v>738</v>
+        <v>48</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="29"/>
+      <c r="H47" s="28"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C48" s="23">
-        <v>5</v>
-      </c>
-      <c r="D48" s="23"/>
+        <v>8</v>
+      </c>
+      <c r="D48" s="23">
+        <v>8</v>
+      </c>
       <c r="E48" s="23"/>
       <c r="F48" s="24" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="29"/>
-    </row>
-    <row r="49" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H48" s="28"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C49" s="23">
-        <v>10</v>
-      </c>
-      <c r="D49" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="D49" s="23">
+        <v>4</v>
+      </c>
       <c r="E49" s="23"/>
       <c r="F49" s="24" t="s">
-        <v>739</v>
+        <v>46</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H49" s="29"/>
+      <c r="H49" s="28"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C50" s="23">
-        <v>3</v>
-      </c>
-      <c r="D50" s="23"/>
+        <v>5</v>
+      </c>
+      <c r="D50" s="23">
+        <v>5</v>
+      </c>
       <c r="E50" s="23"/>
       <c r="F50" s="24" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H50" s="29"/>
+      <c r="H50" s="28"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
-        <v>105</v>
+        <v>22</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C51" s="23">
-        <v>5</v>
-      </c>
-      <c r="D51" s="23">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D51" s="23"/>
       <c r="E51" s="23"/>
       <c r="F51" s="24" t="s">
-        <v>741</v>
+        <v>23</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="29"/>
-    </row>
-    <row r="52" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="H51" s="28"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C52" s="23">
-        <v>4</v>
-      </c>
-      <c r="D52" s="23">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D52" s="23"/>
       <c r="E52" s="23"/>
       <c r="F52" s="24" t="s">
-        <v>742</v>
+        <v>42</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="29"/>
+      <c r="H52" s="28"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C53" s="23">
-        <v>9</v>
-      </c>
-      <c r="D53" s="23">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D53" s="23"/>
       <c r="E53" s="23"/>
       <c r="F53" s="24" t="s">
-        <v>743</v>
+        <v>40</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H53" s="29"/>
+      <c r="H53" s="28"/>
     </row>
     <row r="54" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C54" s="23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D54" s="23">
-        <v>8</v>
-      </c>
-      <c r="E54" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="E54" s="23">
+        <v>6</v>
+      </c>
       <c r="F54" s="24" t="s">
-        <v>744</v>
+        <v>85</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H54" s="29"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H54" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C55" s="23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D55" s="23">
-        <v>9</v>
-      </c>
-      <c r="E55" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="E55" s="23">
+        <v>10</v>
+      </c>
       <c r="F55" s="24" t="s">
-        <v>745</v>
+        <v>90</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H55" s="29"/>
+      <c r="H55" s="28" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C56" s="23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" s="23">
-        <v>7</v>
-      </c>
-      <c r="E56" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="E56" s="23">
+        <v>3</v>
+      </c>
       <c r="F56" s="24" t="s">
-        <v>746</v>
+        <v>62</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="H56" s="29"/>
+      <c r="H56" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9094,51 +9103,51 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="16" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D4" s="15">
         <v>15</v>
@@ -9147,61 +9156,61 @@
         <v>8</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D6" s="15">
         <v>4</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7" s="15">
         <v>3</v>
@@ -9210,42 +9219,42 @@
         <v>1</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D8" s="15">
         <v>4</v>
       </c>
       <c r="E8" s="15"/>
       <c r="F8" s="16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D9" s="15">
         <v>8</v>
@@ -9254,21 +9263,21 @@
         <v>2</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D10" s="15">
         <v>25</v>
@@ -9277,21 +9286,21 @@
         <v>6</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" s="15">
         <v>6</v>
@@ -9300,63 +9309,63 @@
         <v>2</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" s="15">
         <v>4</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D13" s="15">
         <v>8</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="16" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D14" s="15">
         <v>3</v>
@@ -9365,21 +9374,21 @@
         <v>1</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D15" s="15">
         <v>5</v>
@@ -9388,61 +9397,61 @@
         <v>8</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
@@ -9451,21 +9460,21 @@
         <v>2</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
@@ -9474,21 +9483,21 @@
         <v>4</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
@@ -9497,21 +9506,21 @@
         <v>3</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D21" s="15">
         <v>2</v>
@@ -9520,40 +9529,40 @@
         <v>3</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="15">
         <v>10</v>
@@ -9562,52 +9571,52 @@
         <v>8</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D24" s="15">
         <v>8</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="16" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D25" s="15">
         <v>10</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="12" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10700,13 +10709,13 @@
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D2" s="14">
         <v>8</v>
@@ -10715,24 +10724,24 @@
         <v>3</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D3" s="14">
         <v>2</v>
@@ -10741,24 +10750,24 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="14">
         <v>10</v>
@@ -10767,24 +10776,24 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" s="14">
         <v>3</v>
@@ -10793,24 +10802,24 @@
         <v>3</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D6" s="14">
         <v>7</v>
@@ -10819,24 +10828,24 @@
         <v>3</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D7" s="14">
         <v>2</v>
@@ -10845,21 +10854,21 @@
         <v>2</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D8" s="14">
         <v>2</v>
@@ -10868,120 +10877,120 @@
         <v>8</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D9" s="14">
         <v>6</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" s="14">
         <v>2</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D13" s="14">
         <v>5</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D14" s="14">
         <v>6</v>
@@ -10990,122 +10999,122 @@
         <v>4</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D15" s="14">
         <v>5</v>
       </c>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -11114,45 +11123,45 @@
         <v>4</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D21" s="14">
         <v>2</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
@@ -11161,21 +11170,21 @@
         <v>2</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
@@ -11184,40 +11193,40 @@
         <v>2</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
@@ -11226,81 +11235,81 @@
         <v>1</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
@@ -11309,21 +11318,21 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D30" s="14">
         <v>2</v>
@@ -11332,21 +11341,21 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D31" s="14">
         <v>3</v>
@@ -11355,46 +11364,46 @@
         <v>3</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H32" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D33" s="14">
         <v>2</v>
@@ -11403,24 +11412,24 @@
         <v>4</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H33" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D34" s="14">
         <v>6</v>
@@ -11429,271 +11438,271 @@
         <v>6</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H35" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D36" s="14">
         <v>4</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H37" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D42" s="14">
         <v>6</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D43" s="14">
         <v>8</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D44" s="14">
         <v>5</v>
       </c>
       <c r="E44" s="14"/>
       <c r="F44" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D46" s="14">
         <v>8</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D47" s="14">
         <v>8</v>
@@ -11702,43 +11711,43 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H47" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D49" s="14">
         <v>5</v>
@@ -11747,24 +11756,24 @@
         <v>2</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H49" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D50" s="14">
         <v>4</v>
@@ -11773,97 +11782,97 @@
         <v>4</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H50" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="12" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D52" s="14"/>
       <c r="E52" s="14"/>
       <c r="F52" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D53" s="14"/>
       <c r="E53" s="14"/>
       <c r="F53" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C55" s="14"/>
       <c r="D55" s="14">
@@ -11873,21 +11882,21 @@
         <v>8</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H55" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C56" s="14"/>
       <c r="D56" s="14">
@@ -11897,102 +11906,102 @@
         <v>0</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D58" s="14"/>
       <c r="E58" s="14">
         <v>0</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H58" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D60" s="14"/>
       <c r="E60" s="14"/>
       <c r="F60" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D61" s="14">
         <v>25</v>
@@ -12001,10 +12010,10 @@
         <v>15</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12998,13 +13007,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -13013,21 +13022,21 @@
         <v>1</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D3" s="14">
         <v>25</v>
@@ -13036,40 +13045,40 @@
         <v>15</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D5" s="14">
         <v>5</v>
@@ -13078,21 +13087,21 @@
         <v>5</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
@@ -13101,63 +13110,63 @@
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D7" s="14">
         <v>6</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D8" s="14">
         <v>5</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="14">
         <v>4</v>
@@ -13166,42 +13175,42 @@
         <v>4</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D10" s="14">
         <v>5</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D11" s="14">
         <v>9</v>
@@ -13210,59 +13219,59 @@
         <v>5</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D14" s="14">
         <v>1</v>
@@ -13271,21 +13280,21 @@
         <v>3</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
@@ -13294,61 +13303,61 @@
         <v>1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D16" s="14">
         <v>8</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="16" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D18" s="14">
         <v>25</v>
@@ -13357,141 +13366,141 @@
         <v>10</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D21" s="14">
         <v>8</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D22" s="14">
         <v>8</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
@@ -13500,21 +13509,21 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D26" s="14">
         <v>20</v>
@@ -13523,40 +13532,40 @@
         <v>20</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
       <c r="F27" s="12" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
@@ -13565,21 +13574,21 @@
         <v>1</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D29" s="14">
         <v>4</v>
@@ -13588,21 +13597,21 @@
         <v>2</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D30" s="14">
         <v>8</v>
@@ -13611,21 +13620,21 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D31" s="14">
         <v>2</v>
@@ -13634,21 +13643,21 @@
         <v>2</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D32" s="14">
         <v>2</v>
@@ -13657,21 +13666,21 @@
         <v>2</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D33" s="14">
         <v>6</v>
@@ -13680,58 +13689,58 @@
         <v>6</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D34" s="14">
         <v>10</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="12" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14">
@@ -13741,40 +13750,40 @@
         <v>0</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D38" s="14">
         <v>3</v>
@@ -13783,234 +13792,234 @@
         <v>2</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D39" s="14">
         <v>6</v>
       </c>
       <c r="E39" s="14"/>
       <c r="F39" s="12" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="12" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="12" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="12" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="12" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D46" s="8">
         <v>6</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="12" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D50" s="8">
         <v>6</v>
@@ -14019,154 +14028,154 @@
         <v>6</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
       <c r="F55" s="12" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="12" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="12" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D58" s="8">
         <v>25</v>
@@ -14175,10 +14184,10 @@
         <v>10</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -14233,23 +14242,23 @@
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D2" s="14">
         <v>4</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -14271,21 +14280,21 @@
     </row>
     <row r="3" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -14307,21 +14316,21 @@
     </row>
     <row r="4" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -14343,21 +14352,21 @@
     </row>
     <row r="5" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -14379,23 +14388,23 @@
     </row>
     <row r="6" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D6" s="14">
         <v>3</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -14417,13 +14426,13 @@
     </row>
     <row r="7" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D7" s="14">
         <v>1</v>
@@ -14432,10 +14441,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -14457,21 +14466,21 @@
     </row>
     <row r="8" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -14493,21 +14502,21 @@
     </row>
     <row r="9" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -14529,23 +14538,23 @@
     </row>
     <row r="10" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" s="14">
         <v>6</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -14567,13 +14576,13 @@
     </row>
     <row r="11" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D11" s="14">
         <v>6</v>
@@ -14582,10 +14591,10 @@
         <v>3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -14607,13 +14616,13 @@
     </row>
     <row r="12" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D12" s="14">
         <v>2</v>
@@ -14622,10 +14631,10 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -14647,23 +14656,23 @@
     </row>
     <row r="13" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13" s="14">
         <v>7</v>
       </c>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -14685,13 +14694,13 @@
     </row>
     <row r="14" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D14" s="14">
         <v>5</v>
@@ -14700,10 +14709,10 @@
         <v>7</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -14725,21 +14734,21 @@
     </row>
     <row r="15" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -14761,13 +14770,13 @@
     </row>
     <row r="16" spans="1:24" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D16" s="14">
         <v>35</v>
@@ -14776,10 +14785,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -14801,21 +14810,21 @@
     </row>
     <row r="17" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -14837,23 +14846,23 @@
     </row>
     <row r="18" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D18" s="14">
         <v>10</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -14875,21 +14884,21 @@
     </row>
     <row r="19" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="12" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -14911,13 +14920,13 @@
     </row>
     <row r="20" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
@@ -14926,10 +14935,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -14951,21 +14960,21 @@
     </row>
     <row r="21" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -14987,21 +14996,21 @@
     </row>
     <row r="22" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -15023,21 +15032,21 @@
     </row>
     <row r="23" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -15059,21 +15068,21 @@
     </row>
     <row r="24" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="12" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -15095,13 +15104,13 @@
     </row>
     <row r="25" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
@@ -15110,10 +15119,10 @@
         <v>2</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -15135,21 +15144,21 @@
     </row>
     <row r="26" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
       <c r="F26" s="12" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -15171,10 +15180,10 @@
     </row>
     <row r="27" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14">
@@ -15184,10 +15193,10 @@
         <v>1</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -15209,19 +15218,19 @@
     </row>
     <row r="28" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="12" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -15243,13 +15252,13 @@
     </row>
     <row r="29" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D29" s="14">
         <v>4</v>
@@ -15258,10 +15267,10 @@
         <v>4</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -15283,13 +15292,13 @@
     </row>
     <row r="30" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D30" s="14">
         <v>30</v>
@@ -15298,10 +15307,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -15323,23 +15332,23 @@
     </row>
     <row r="31" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D31" s="8">
         <v>5</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -15361,21 +15370,21 @@
     </row>
     <row r="32" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -15397,23 +15406,23 @@
     </row>
     <row r="33" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D33" s="8">
         <v>8</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="13" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -15435,23 +15444,23 @@
     </row>
     <row r="34" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D34" s="8">
         <v>6</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="13" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -15473,13 +15482,13 @@
     </row>
     <row r="35" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D35" s="8">
         <v>3</v>
@@ -15488,10 +15497,10 @@
         <v>6</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -15513,13 +15522,13 @@
     </row>
     <row r="36" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D36" s="8">
         <v>7</v>
@@ -15528,10 +15537,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -15553,21 +15562,21 @@
     </row>
     <row r="37" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="13" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -21176,13 +21185,13 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D2" s="14">
         <v>7</v>
@@ -21191,21 +21200,21 @@
         <v>7</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D3" s="14">
         <v>3</v>
@@ -21214,42 +21223,42 @@
         <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D4" s="14">
         <v>5</v>
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D5" s="14">
         <v>8</v>
@@ -21258,103 +21267,103 @@
         <v>6</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="14">
         <v>5</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D7" s="14">
         <v>10</v>
       </c>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D8" s="14">
         <v>8</v>
       </c>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D10" s="14">
         <v>6</v>
@@ -21363,21 +21372,21 @@
         <v>6</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" s="14">
         <v>4</v>
@@ -21386,152 +21395,152 @@
         <v>4</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D19" s="14">
         <v>1</v>
@@ -21540,103 +21549,103 @@
         <v>6</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D20" s="14">
         <v>10</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D21" s="14">
         <v>1</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D23" s="14">
         <v>8</v>
       </c>
       <c r="E23" s="14"/>
       <c r="F23" s="12" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D24" s="14">
         <v>5</v>
@@ -21645,31 +21654,31 @@
         <v>5</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="12" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24251,336 +24260,336 @@
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
       <c r="F2" s="12" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="12" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
       <c r="F6" s="12" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
       <c r="F7" s="12" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="12" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="12" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="12" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
       <c r="F11" s="12" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
       <c r="F12" s="12" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="12" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
       <c r="F14" s="12" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
       <c r="F16" s="12" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
       <c r="F17" s="12" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="12" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D19" s="14">
         <v>5</v>
@@ -24589,67 +24598,67 @@
         <v>2</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="12" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
       <c r="F22" s="12" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
